--- a/datadescrip/datos_actfisica_flexibilidad.xlsx
+++ b/datadescrip/datos_actfisica_flexibilidad.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Datos\datadescrip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C6F4A50-3373-4284-86A7-68CAB6CC5892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2BD95BB-DA10-4E40-B9AE-76DD1760F452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,31 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="33">
   <si>
-    <t>Institución</t>
-  </si>
-  <si>
-    <t>Edad 1er tamizaje en años</t>
-  </si>
-  <si>
-    <t>sexo</t>
-  </si>
-  <si>
-    <t>Grado Escolar 1er Tamizaje</t>
-  </si>
-  <si>
-    <t>Clasificación nutricional</t>
-  </si>
-  <si>
-    <t>Estatura (cm)</t>
-  </si>
-  <si>
-    <t>Peso (kg)</t>
-  </si>
-  <si>
     <t>Flexibilidad</t>
-  </si>
-  <si>
-    <t>Nivel de AF</t>
   </si>
   <si>
     <t>SANTUARIO</t>
@@ -123,6 +99,30 @@
   </si>
   <si>
     <t>Prioridad</t>
+  </si>
+  <si>
+    <t>Actividad_Fisica</t>
+  </si>
+  <si>
+    <t>Peso_kg</t>
+  </si>
+  <si>
+    <t>Estatura_cm</t>
+  </si>
+  <si>
+    <t>Grado_Escolar</t>
+  </si>
+  <si>
+    <t>Clasificacion_Nutricional</t>
+  </si>
+  <si>
+    <t>Sexo</t>
+  </si>
+  <si>
+    <t>Edad_1er_tamizaje_en_anios</t>
+  </si>
+  <si>
+    <t>Institucion</t>
   </si>
 </sst>
 </file>
@@ -470,48 +470,48 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B2">
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F2">
         <v>114.3</v>
@@ -520,27 +520,27 @@
         <v>19.8</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B3">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F3">
         <v>114.4</v>
@@ -549,27 +549,27 @@
         <v>20.8</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B4">
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F4">
         <v>114.4</v>
@@ -578,27 +578,27 @@
         <v>22.4</v>
       </c>
       <c r="H4" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I4" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B5">
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F5">
         <v>122.7</v>
@@ -607,27 +607,27 @@
         <v>22.9</v>
       </c>
       <c r="H5" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F6">
         <v>113.9</v>
@@ -636,27 +636,27 @@
         <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I6" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B7">
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F7">
         <v>127.2</v>
@@ -665,27 +665,27 @@
         <v>31.6</v>
       </c>
       <c r="H7" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B8">
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F8">
         <v>118.3</v>
@@ -694,27 +694,27 @@
         <v>21.5</v>
       </c>
       <c r="H8" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I8" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B9">
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F9">
         <v>111.3</v>
@@ -723,27 +723,27 @@
         <v>13.6</v>
       </c>
       <c r="H9" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I9" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B10">
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F10">
         <v>116.2</v>
@@ -752,27 +752,27 @@
         <v>22.1</v>
       </c>
       <c r="H10" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I10" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F11">
         <v>116.2</v>
@@ -781,27 +781,27 @@
         <v>17.8</v>
       </c>
       <c r="H11" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I11" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B12">
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F12">
         <v>134.69999999999999</v>
@@ -810,27 +810,27 @@
         <v>23.1</v>
       </c>
       <c r="H12" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I12" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B13">
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F13">
         <v>114.4</v>
@@ -839,27 +839,27 @@
         <v>24.5</v>
       </c>
       <c r="H13" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I13" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B14">
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D14" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F14">
         <v>120.4</v>
@@ -868,27 +868,27 @@
         <v>21.9</v>
       </c>
       <c r="H14" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I14" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B15">
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F15">
         <v>122.9</v>
@@ -897,27 +897,27 @@
         <v>23.6</v>
       </c>
       <c r="H15" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I15" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B16">
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F16">
         <v>118.9</v>
@@ -926,27 +926,27 @@
         <v>24.6</v>
       </c>
       <c r="H16" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I16" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B17">
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F17">
         <v>117.8</v>
@@ -955,27 +955,27 @@
         <v>19.600000000000001</v>
       </c>
       <c r="H17" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I17" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B18">
         <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E18" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F18">
         <v>102.9</v>
@@ -984,27 +984,27 @@
         <v>13.6</v>
       </c>
       <c r="H18" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I18" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B19">
         <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D19" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E19" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F19">
         <v>110.4</v>
@@ -1013,27 +1013,27 @@
         <v>19.5</v>
       </c>
       <c r="H19" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I19" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B20">
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E20" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F20">
         <v>118.3</v>
@@ -1042,27 +1042,27 @@
         <v>15.4</v>
       </c>
       <c r="H20" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I20" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B21">
         <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E21" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F21">
         <v>119.2</v>
@@ -1071,27 +1071,27 @@
         <v>24.9</v>
       </c>
       <c r="H21" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I21" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B22">
         <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E22" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F22">
         <v>115.6</v>
@@ -1100,27 +1100,27 @@
         <v>20.100000000000001</v>
       </c>
       <c r="H22" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I22" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B23">
         <v>6</v>
       </c>
       <c r="C23" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E23" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F23">
         <v>115.6</v>
@@ -1129,27 +1129,27 @@
         <v>17.3</v>
       </c>
       <c r="H23" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I23" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B24">
         <v>0</v>
       </c>
       <c r="C24" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D24" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E24" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F24">
         <v>118.2</v>
@@ -1158,27 +1158,27 @@
         <v>21.8</v>
       </c>
       <c r="H24" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I24" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B25">
         <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D25" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E25" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F25">
         <v>118.2</v>
@@ -1187,27 +1187,27 @@
         <v>21.9</v>
       </c>
       <c r="H25" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I25" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E26" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F26">
         <v>112.9</v>
@@ -1216,27 +1216,27 @@
         <v>26.4</v>
       </c>
       <c r="H26" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I26" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B27">
         <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E27" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F27">
         <v>113.7</v>
@@ -1245,27 +1245,27 @@
         <v>20.3</v>
       </c>
       <c r="H27" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I27" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B28">
         <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E28" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F28">
         <v>114.7</v>
@@ -1274,27 +1274,27 @@
         <v>26.5</v>
       </c>
       <c r="H28" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I28" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B29">
         <v>0</v>
       </c>
       <c r="C29" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E29" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F29">
         <v>111.9</v>
@@ -1303,27 +1303,27 @@
         <v>18.100000000000001</v>
       </c>
       <c r="H29" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I29" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B30">
         <v>9</v>
       </c>
       <c r="C30" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D30" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E30" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F30">
         <v>135.80000000000001</v>
@@ -1332,27 +1332,27 @@
         <v>42.5</v>
       </c>
       <c r="H30" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I30" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B31">
         <v>6</v>
       </c>
       <c r="C31" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D31" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E31" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F31">
         <v>117.5</v>
@@ -1361,27 +1361,27 @@
         <v>22</v>
       </c>
       <c r="H31" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I31" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B32">
         <v>8</v>
       </c>
       <c r="C32" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D32" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E32" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F32">
         <v>133.1</v>
@@ -1390,27 +1390,27 @@
         <v>27.5</v>
       </c>
       <c r="H32" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I32" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B33">
         <v>11</v>
       </c>
       <c r="C33" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D33" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E33" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F33">
         <v>108.9</v>
@@ -1419,27 +1419,27 @@
         <v>17.600000000000001</v>
       </c>
       <c r="H33" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I33" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B34">
         <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D34" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E34" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F34">
         <v>131.80000000000001</v>
@@ -1448,27 +1448,27 @@
         <v>25.1</v>
       </c>
       <c r="H34" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I34" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B35">
         <v>7</v>
       </c>
       <c r="C35" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D35" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E35" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F35">
         <v>122.2</v>
@@ -1477,27 +1477,27 @@
         <v>23.3</v>
       </c>
       <c r="H35" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I35" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
       <c r="C36" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D36" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E36" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F36">
         <v>114.4</v>
@@ -1506,27 +1506,27 @@
         <v>20.8</v>
       </c>
       <c r="H36" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I36" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
       <c r="C37" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D37" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E37" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F37">
         <v>118.9</v>
@@ -1535,27 +1535,27 @@
         <v>21.4</v>
       </c>
       <c r="H37" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I37" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B38">
         <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D38" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E38" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F38">
         <v>118.1</v>
@@ -1564,27 +1564,27 @@
         <v>29</v>
       </c>
       <c r="H38" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I38" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B39">
         <v>0</v>
       </c>
       <c r="C39" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D39" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E39" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F39">
         <v>112.2</v>
@@ -1593,27 +1593,27 @@
         <v>18.399999999999999</v>
       </c>
       <c r="H39" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I39" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D40" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E40" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F40">
         <v>120.8</v>
@@ -1622,27 +1622,27 @@
         <v>21.7</v>
       </c>
       <c r="H40" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I40" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
       <c r="C41" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D41" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E41" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F41">
         <v>115.6</v>
@@ -1651,27 +1651,27 @@
         <v>25.3</v>
       </c>
       <c r="H41" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I41" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B42">
         <v>0</v>
       </c>
       <c r="C42" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D42" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E42" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F42">
         <v>111.4</v>
@@ -1680,27 +1680,27 @@
         <v>18.7</v>
       </c>
       <c r="H42" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I42" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B43">
         <v>11</v>
       </c>
       <c r="C43" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D43" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E43" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F43">
         <v>106.8</v>
@@ -1709,27 +1709,27 @@
         <v>16.5</v>
       </c>
       <c r="H43" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I43" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B44">
         <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D44" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E44" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F44">
         <v>112.2</v>
@@ -1738,27 +1738,27 @@
         <v>14</v>
       </c>
       <c r="H44" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I44" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B45">
         <v>8</v>
       </c>
       <c r="C45" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D45" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E45" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F45">
         <v>133</v>
@@ -1767,27 +1767,27 @@
         <v>32.9</v>
       </c>
       <c r="H45" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I45" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B46">
         <v>9</v>
       </c>
       <c r="C46" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D46" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E46" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F46">
         <v>134.30000000000001</v>
@@ -1796,27 +1796,27 @@
         <v>28.9</v>
       </c>
       <c r="H46" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I46" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B47">
         <v>8</v>
       </c>
       <c r="C47" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D47" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E47" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F47">
         <v>132.4</v>
@@ -1825,27 +1825,27 @@
         <v>28.6</v>
       </c>
       <c r="H47" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I47" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B48">
         <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D48" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E48" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F48">
         <v>117.4</v>
@@ -1854,27 +1854,27 @@
         <v>20</v>
       </c>
       <c r="H48" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I48" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B49">
         <v>6</v>
       </c>
       <c r="C49" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D49" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E49" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F49">
         <v>119.5</v>
@@ -1883,27 +1883,27 @@
         <v>16.600000000000001</v>
       </c>
       <c r="H49" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I49" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B50">
         <v>6</v>
       </c>
       <c r="C50" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D50" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E50" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F50">
         <v>121.1</v>
@@ -1912,27 +1912,27 @@
         <v>31.2</v>
       </c>
       <c r="H50" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I50" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B51">
         <v>6</v>
       </c>
       <c r="C51" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D51" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E51" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F51">
         <v>124.8</v>
@@ -1941,27 +1941,27 @@
         <v>23.4</v>
       </c>
       <c r="H51" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I51" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B52">
         <v>6</v>
       </c>
       <c r="C52" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D52" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E52" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F52">
         <v>123</v>
@@ -1970,27 +1970,27 @@
         <v>23.3</v>
       </c>
       <c r="H52" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I52" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B53">
         <v>10</v>
       </c>
       <c r="C53" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D53" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E53" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F53">
         <v>113.4</v>
@@ -1999,27 +1999,27 @@
         <v>18.5</v>
       </c>
       <c r="H53" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I53" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B54">
         <v>9</v>
       </c>
       <c r="C54" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D54" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E54" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F54">
         <v>132.19999999999999</v>
@@ -2028,27 +2028,27 @@
         <v>29.8</v>
       </c>
       <c r="H54" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I54" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B55">
         <v>6</v>
       </c>
       <c r="C55" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D55" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E55" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F55">
         <v>120.1</v>
@@ -2057,27 +2057,27 @@
         <v>27.2</v>
       </c>
       <c r="H55" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I55" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B56">
         <v>7</v>
       </c>
       <c r="C56" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D56" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E56" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F56">
         <v>109.1</v>
@@ -2086,27 +2086,27 @@
         <v>26.1</v>
       </c>
       <c r="H56" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I56" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B57">
         <v>9</v>
       </c>
       <c r="C57" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D57" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E57" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F57">
         <v>135.80000000000001</v>
@@ -2115,27 +2115,27 @@
         <v>28.5</v>
       </c>
       <c r="H57" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I57" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B58">
         <v>7</v>
       </c>
       <c r="C58" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D58" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E58" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F58">
         <v>118.9</v>
@@ -2144,27 +2144,27 @@
         <v>21.8</v>
       </c>
       <c r="H58" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I58" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B59">
         <v>6</v>
       </c>
       <c r="C59" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D59" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E59" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F59">
         <v>123.6</v>
@@ -2173,27 +2173,27 @@
         <v>16.8</v>
       </c>
       <c r="H59" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I59" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B60">
         <v>6</v>
       </c>
       <c r="C60" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D60" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E60" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F60">
         <v>112.9</v>
@@ -2202,27 +2202,27 @@
         <v>20.9</v>
       </c>
       <c r="H60" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I60" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B61">
         <v>5</v>
       </c>
       <c r="C61" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D61" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E61" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F61">
         <v>112.8</v>
@@ -2231,27 +2231,27 @@
         <v>19.100000000000001</v>
       </c>
       <c r="H61" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I61" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B62">
         <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D62" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E62" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F62">
         <v>126.5</v>
@@ -2260,27 +2260,27 @@
         <v>28.2</v>
       </c>
       <c r="H62" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I62" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B63">
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D63" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E63" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F63">
         <v>128.1</v>
@@ -2289,27 +2289,27 @@
         <v>20.7</v>
       </c>
       <c r="H63" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I63" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B64">
         <v>6</v>
       </c>
       <c r="C64" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E64" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F64">
         <v>120.4</v>
@@ -2318,27 +2318,27 @@
         <v>22.2</v>
       </c>
       <c r="H64" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I64" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B65">
         <v>6</v>
       </c>
       <c r="C65" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D65" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E65" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F65">
         <v>126.4</v>
@@ -2347,27 +2347,27 @@
         <v>24.8</v>
       </c>
       <c r="H65" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I65" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B66">
         <v>6</v>
       </c>
       <c r="C66" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E66" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F66">
         <v>122.8</v>
@@ -2376,27 +2376,27 @@
         <v>21.5</v>
       </c>
       <c r="H66" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I66" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B67">
         <v>11</v>
       </c>
       <c r="C67" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D67" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E67" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F67">
         <v>114.4</v>
@@ -2405,27 +2405,27 @@
         <v>24.3</v>
       </c>
       <c r="H67" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I67" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B68">
         <v>5</v>
       </c>
       <c r="C68" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E68" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F68">
         <v>124.7</v>
@@ -2434,27 +2434,27 @@
         <v>21.7</v>
       </c>
       <c r="H68" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I68" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B69">
         <v>9</v>
       </c>
       <c r="C69" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E69" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F69">
         <v>138</v>
@@ -2463,27 +2463,27 @@
         <v>31.2</v>
       </c>
       <c r="H69" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I69" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B70">
         <v>5</v>
       </c>
       <c r="C70" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D70" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E70" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F70">
         <v>123.7</v>
@@ -2492,27 +2492,27 @@
         <v>19.7</v>
       </c>
       <c r="H70" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I70" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B71">
         <v>10</v>
       </c>
       <c r="C71" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D71" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E71" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F71">
         <v>115.3</v>
@@ -2521,27 +2521,27 @@
         <v>19.8</v>
       </c>
       <c r="H71" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I71" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B72">
         <v>8</v>
       </c>
       <c r="C72" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D72" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E72" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F72">
         <v>119.8</v>
@@ -2550,27 +2550,27 @@
         <v>22.6</v>
       </c>
       <c r="H72" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I72" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B73">
         <v>8</v>
       </c>
       <c r="C73" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D73" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E73" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F73">
         <v>126</v>
@@ -2579,27 +2579,27 @@
         <v>27.3</v>
       </c>
       <c r="H73" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I73" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B74">
         <v>6</v>
       </c>
       <c r="C74" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D74" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E74" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F74">
         <v>112.9</v>
@@ -2608,27 +2608,27 @@
         <v>19.8</v>
       </c>
       <c r="H74" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I74" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B75">
         <v>10</v>
       </c>
       <c r="C75" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D75" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E75" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F75">
         <v>108.2</v>
@@ -2637,27 +2637,27 @@
         <v>17.5</v>
       </c>
       <c r="H75" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I75" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B76">
         <v>11</v>
       </c>
       <c r="C76" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D76" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E76" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F76">
         <v>117.3</v>
@@ -2666,27 +2666,27 @@
         <v>26.1</v>
       </c>
       <c r="H76" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I76" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B77">
         <v>9</v>
       </c>
       <c r="C77" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D77" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E77" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F77">
         <v>140.19999999999999</v>
@@ -2695,27 +2695,27 @@
         <v>31.2</v>
       </c>
       <c r="H77" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I77" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B78">
         <v>9</v>
       </c>
       <c r="C78" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D78" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E78" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F78">
         <v>126.4</v>
@@ -2724,27 +2724,27 @@
         <v>30.8</v>
       </c>
       <c r="H78" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I78" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B79">
         <v>11</v>
       </c>
       <c r="C79" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D79" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E79" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F79">
         <v>118.6</v>
@@ -2753,27 +2753,27 @@
         <v>22.1</v>
       </c>
       <c r="H79" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I79" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B80">
         <v>8</v>
       </c>
       <c r="C80" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D80" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E80" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F80">
         <v>123.5</v>
@@ -2782,27 +2782,27 @@
         <v>22.1</v>
       </c>
       <c r="H80" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I80" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B81">
         <v>5</v>
       </c>
       <c r="C81" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D81" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E81" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F81">
         <v>116.4</v>
@@ -2811,27 +2811,27 @@
         <v>21.5</v>
       </c>
       <c r="H81" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I81" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B82">
         <v>10</v>
       </c>
       <c r="C82" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D82" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E82" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F82">
         <v>144.4</v>
@@ -2840,27 +2840,27 @@
         <v>41.3</v>
       </c>
       <c r="H82" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I82" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B83">
         <v>9</v>
       </c>
       <c r="C83" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D83" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E83" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F83">
         <v>134.4</v>
@@ -2869,27 +2869,27 @@
         <v>37.299999999999997</v>
       </c>
       <c r="H83" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I83" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B84">
         <v>5</v>
       </c>
       <c r="C84" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D84" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E84" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F84">
         <v>117.2</v>
@@ -2898,27 +2898,27 @@
         <v>20.7</v>
       </c>
       <c r="H84" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I84" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B85">
         <v>10</v>
       </c>
       <c r="C85" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D85" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E85" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F85">
         <v>138.6</v>
@@ -2927,27 +2927,27 @@
         <v>45.1</v>
       </c>
       <c r="H85" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I85" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B86">
         <v>7</v>
       </c>
       <c r="C86" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D86" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E86" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F86">
         <v>122.6</v>
@@ -2956,27 +2956,27 @@
         <v>23.8</v>
       </c>
       <c r="H86" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I86" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B87">
         <v>9</v>
       </c>
       <c r="C87" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D87" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E87" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F87">
         <v>138</v>
@@ -2985,27 +2985,27 @@
         <v>35.200000000000003</v>
       </c>
       <c r="H87" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I87" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B88">
         <v>10</v>
       </c>
       <c r="C88" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D88" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E88" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F88">
         <v>129.4</v>
@@ -3014,27 +3014,27 @@
         <v>24.3</v>
       </c>
       <c r="H88" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I88" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B89">
         <v>7</v>
       </c>
       <c r="C89" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D89" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E89" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F89">
         <v>122.1</v>
@@ -3043,27 +3043,27 @@
         <v>22.2</v>
       </c>
       <c r="H89" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I89" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B90">
         <v>10</v>
       </c>
       <c r="C90" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D90" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E90" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F90">
         <v>142.4</v>
@@ -3072,27 +3072,27 @@
         <v>34</v>
       </c>
       <c r="H90" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I90" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B91">
         <v>5</v>
       </c>
       <c r="C91" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D91" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E91" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F91">
         <v>110</v>
@@ -3101,27 +3101,27 @@
         <v>19</v>
       </c>
       <c r="H91" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I91" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B92">
         <v>8</v>
       </c>
       <c r="C92" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D92" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E92" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F92">
         <v>126</v>
@@ -3130,27 +3130,27 @@
         <v>19.7</v>
       </c>
       <c r="H92" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I92" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B93">
         <v>7</v>
       </c>
       <c r="C93" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D93" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E93" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F93">
         <v>124.3</v>
@@ -3159,27 +3159,27 @@
         <v>23.7</v>
       </c>
       <c r="H93" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I93" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B94">
         <v>10</v>
       </c>
       <c r="C94" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D94" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E94" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F94">
         <v>134.30000000000001</v>
@@ -3188,27 +3188,27 @@
         <v>30.2</v>
       </c>
       <c r="H94" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I94" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B95">
         <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D95" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E95" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F95">
         <v>129.4</v>
@@ -3217,27 +3217,27 @@
         <v>25.3</v>
       </c>
       <c r="H95" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I95" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B96">
         <v>5</v>
       </c>
       <c r="C96" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E96" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F96">
         <v>118</v>
@@ -3246,27 +3246,27 @@
         <v>22.4</v>
       </c>
       <c r="H96" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I96" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B97">
         <v>5</v>
       </c>
       <c r="C97" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D97" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E97" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F97">
         <v>111.4</v>
@@ -3275,27 +3275,27 @@
         <v>19.399999999999999</v>
       </c>
       <c r="H97" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I97" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B98">
         <v>6</v>
       </c>
       <c r="C98" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E98" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F98">
         <v>116</v>
@@ -3304,27 +3304,27 @@
         <v>23</v>
       </c>
       <c r="H98" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I98" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B99">
         <v>7</v>
       </c>
       <c r="C99" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D99" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E99" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F99">
         <v>111.7</v>
@@ -3333,27 +3333,27 @@
         <v>19.899999999999999</v>
       </c>
       <c r="H99" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I99" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B100">
         <v>10</v>
       </c>
       <c r="C100" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E100" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F100">
         <v>136.5</v>
@@ -3362,27 +3362,27 @@
         <v>35.799999999999997</v>
       </c>
       <c r="H100" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I100" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B101">
         <v>7</v>
       </c>
       <c r="C101" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D101" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E101" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F101">
         <v>130.5</v>
@@ -3391,27 +3391,27 @@
         <v>18.7</v>
       </c>
       <c r="H101" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I101" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B102">
         <v>7</v>
       </c>
       <c r="C102" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D102" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E102" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F102">
         <v>132.19999999999999</v>
@@ -3420,27 +3420,27 @@
         <v>26.3</v>
       </c>
       <c r="H102" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I102" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B103">
         <v>7</v>
       </c>
       <c r="C103" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D103" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E103" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F103">
         <v>122.8</v>
@@ -3449,27 +3449,27 @@
         <v>22.6</v>
       </c>
       <c r="H103" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I103" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B104">
         <v>8</v>
       </c>
       <c r="C104" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E104" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F104">
         <v>123.5</v>
@@ -3478,27 +3478,27 @@
         <v>28.4</v>
       </c>
       <c r="H104" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I104" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B105">
         <v>10</v>
       </c>
       <c r="C105" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D105" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E105" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F105">
         <v>136.6</v>
@@ -3507,27 +3507,27 @@
         <v>30.7</v>
       </c>
       <c r="H105" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I105" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B106">
         <v>10</v>
       </c>
       <c r="C106" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D106" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E106" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F106">
         <v>127.5</v>
@@ -3536,27 +3536,27 @@
         <v>25.9</v>
       </c>
       <c r="H106" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I106" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B107">
         <v>10</v>
       </c>
       <c r="C107" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D107" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E107" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F107">
         <v>137.19999999999999</v>
@@ -3565,27 +3565,27 @@
         <v>33.299999999999997</v>
       </c>
       <c r="H107" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I107" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B108">
         <v>10</v>
       </c>
       <c r="C108" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D108" t="s">
+        <v>15</v>
+      </c>
+      <c r="E108" t="s">
         <v>23</v>
-      </c>
-      <c r="E108" t="s">
-        <v>31</v>
       </c>
       <c r="F108">
         <v>133</v>
@@ -3594,27 +3594,27 @@
         <v>34.6</v>
       </c>
       <c r="H108" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I108" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B109">
         <v>10</v>
       </c>
       <c r="C109" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D109" t="s">
+        <v>15</v>
+      </c>
+      <c r="E109" t="s">
         <v>23</v>
-      </c>
-      <c r="E109" t="s">
-        <v>31</v>
       </c>
       <c r="F109">
         <v>153.80000000000001</v>
@@ -3623,27 +3623,27 @@
         <v>51.1</v>
       </c>
       <c r="H109" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I109" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B110">
         <v>10</v>
       </c>
       <c r="C110" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D110" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E110" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F110">
         <v>130.5</v>
@@ -3652,27 +3652,27 @@
         <v>27</v>
       </c>
       <c r="H110" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I110" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B111">
         <v>10</v>
       </c>
       <c r="C111" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D111" t="s">
+        <v>15</v>
+      </c>
+      <c r="E111" t="s">
         <v>23</v>
-      </c>
-      <c r="E111" t="s">
-        <v>31</v>
       </c>
       <c r="F111">
         <v>140.4</v>
@@ -3681,27 +3681,27 @@
         <v>39.1</v>
       </c>
       <c r="H111" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I111" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B112">
         <v>10</v>
       </c>
       <c r="C112" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D112" t="s">
+        <v>15</v>
+      </c>
+      <c r="E112" t="s">
         <v>23</v>
-      </c>
-      <c r="E112" t="s">
-        <v>31</v>
       </c>
       <c r="F112">
         <v>144.5</v>
@@ -3710,27 +3710,27 @@
         <v>46.1</v>
       </c>
       <c r="H112" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I112" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B113">
         <v>10</v>
       </c>
       <c r="C113" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D113" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E113" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F113">
         <v>130</v>
@@ -3739,27 +3739,27 @@
         <v>27</v>
       </c>
       <c r="H113" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I113" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B114">
         <v>9</v>
       </c>
       <c r="C114" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D114" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E114" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F114">
         <v>138.19999999999999</v>
@@ -3768,27 +3768,27 @@
         <v>31.1</v>
       </c>
       <c r="H114" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I114" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B115">
         <v>10</v>
       </c>
       <c r="C115" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D115" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E115" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F115">
         <v>128.19999999999999</v>
@@ -3797,27 +3797,27 @@
         <v>26.7</v>
       </c>
       <c r="H115" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I115" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B116">
         <v>10</v>
       </c>
       <c r="C116" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D116" t="s">
+        <v>15</v>
+      </c>
+      <c r="E116" t="s">
         <v>23</v>
-      </c>
-      <c r="E116" t="s">
-        <v>31</v>
       </c>
       <c r="F116">
         <v>145</v>
@@ -3826,27 +3826,27 @@
         <v>44.2</v>
       </c>
       <c r="H116" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I116" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B117">
         <v>10</v>
       </c>
       <c r="C117" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D117" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E117" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F117">
         <v>140.80000000000001</v>
@@ -3855,27 +3855,27 @@
         <v>32.799999999999997</v>
       </c>
       <c r="H117" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I117" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B118">
         <v>10</v>
       </c>
       <c r="C118" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D118" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E118" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F118">
         <v>131.80000000000001</v>
@@ -3884,27 +3884,27 @@
         <v>27.1</v>
       </c>
       <c r="H118" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I118" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B119">
         <v>7</v>
       </c>
       <c r="C119" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D119" t="s">
+        <v>15</v>
+      </c>
+      <c r="E119" t="s">
         <v>23</v>
-      </c>
-      <c r="E119" t="s">
-        <v>31</v>
       </c>
       <c r="F119">
         <v>138.19999999999999</v>
@@ -3913,27 +3913,27 @@
         <v>43.4</v>
       </c>
       <c r="H119" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I119" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B120">
         <v>11</v>
       </c>
       <c r="C120" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D120" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E120" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F120">
         <v>146.9</v>
@@ -3942,27 +3942,27 @@
         <v>35.4</v>
       </c>
       <c r="H120" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I120" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B121">
         <v>6</v>
       </c>
       <c r="C121" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D121" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E121" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F121">
         <v>132.19999999999999</v>
@@ -3971,27 +3971,27 @@
         <v>27.4</v>
       </c>
       <c r="H121" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I121" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B122">
         <v>7</v>
       </c>
       <c r="C122" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D122" t="s">
+        <v>15</v>
+      </c>
+      <c r="E122" t="s">
         <v>23</v>
-      </c>
-      <c r="E122" t="s">
-        <v>31</v>
       </c>
       <c r="F122">
         <v>132.19999999999999</v>
@@ -4000,27 +4000,27 @@
         <v>39.9</v>
       </c>
       <c r="H122" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I122" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B123">
         <v>6</v>
       </c>
       <c r="C123" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D123" t="s">
+        <v>15</v>
+      </c>
+      <c r="E123" t="s">
         <v>23</v>
-      </c>
-      <c r="E123" t="s">
-        <v>31</v>
       </c>
       <c r="F123">
         <v>126.4</v>
@@ -4029,27 +4029,27 @@
         <v>35.200000000000003</v>
       </c>
       <c r="H123" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I123" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B124">
         <v>11</v>
       </c>
       <c r="C124" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D124" t="s">
+        <v>15</v>
+      </c>
+      <c r="E124" t="s">
         <v>23</v>
-      </c>
-      <c r="E124" t="s">
-        <v>31</v>
       </c>
       <c r="F124">
         <v>146.19999999999999</v>
@@ -4058,27 +4058,27 @@
         <v>44.9</v>
       </c>
       <c r="H124" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I124" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B125">
         <v>11</v>
       </c>
       <c r="C125" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D125" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E125" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F125">
         <v>144.4</v>
@@ -4087,27 +4087,27 @@
         <v>32.5</v>
       </c>
       <c r="H125" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I125" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B126">
         <v>11</v>
       </c>
       <c r="C126" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D126" t="s">
+        <v>15</v>
+      </c>
+      <c r="E126" t="s">
         <v>23</v>
-      </c>
-      <c r="E126" t="s">
-        <v>31</v>
       </c>
       <c r="F126">
         <v>142</v>
@@ -4116,27 +4116,27 @@
         <v>44.8</v>
       </c>
       <c r="H126" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I126" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B127">
         <v>8</v>
       </c>
       <c r="C127" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D127" t="s">
+        <v>15</v>
+      </c>
+      <c r="E127" t="s">
         <v>23</v>
-      </c>
-      <c r="E127" t="s">
-        <v>31</v>
       </c>
       <c r="F127">
         <v>122.6</v>
@@ -4145,27 +4145,27 @@
         <v>34.299999999999997</v>
       </c>
       <c r="H127" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I127" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B128">
         <v>11</v>
       </c>
       <c r="C128" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D128" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E128" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F128">
         <v>149</v>
@@ -4174,27 +4174,27 @@
         <v>38.200000000000003</v>
       </c>
       <c r="H128" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I128" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B129">
         <v>10</v>
       </c>
       <c r="C129" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D129" t="s">
+        <v>15</v>
+      </c>
+      <c r="E129" t="s">
         <v>23</v>
-      </c>
-      <c r="E129" t="s">
-        <v>31</v>
       </c>
       <c r="F129">
         <v>154.69999999999999</v>
@@ -4203,27 +4203,27 @@
         <v>46.1</v>
       </c>
       <c r="H129" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I129" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B130">
         <v>6</v>
       </c>
       <c r="C130" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D130" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E130" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F130">
         <v>141.1</v>
@@ -4232,27 +4232,27 @@
         <v>32.9</v>
       </c>
       <c r="H130" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I130" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B131">
         <v>10</v>
       </c>
       <c r="C131" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D131" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E131" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F131">
         <v>136.9</v>
@@ -4261,27 +4261,27 @@
         <v>34</v>
       </c>
       <c r="H131" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I131" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B132">
         <v>10</v>
       </c>
       <c r="C132" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D132" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E132" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F132">
         <v>145.5</v>
@@ -4290,27 +4290,27 @@
         <v>27.9</v>
       </c>
       <c r="H132" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I132" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B133">
         <v>11</v>
       </c>
       <c r="C133" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D133" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E133" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F133">
         <v>142</v>
@@ -4319,27 +4319,27 @@
         <v>34.6</v>
       </c>
       <c r="H133" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I133" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B134">
         <v>9</v>
       </c>
       <c r="C134" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D134" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E134" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F134">
         <v>135.9</v>
@@ -4348,27 +4348,27 @@
         <v>27.4</v>
       </c>
       <c r="H134" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I134" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B135">
         <v>9</v>
       </c>
       <c r="C135" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D135" t="s">
+        <v>15</v>
+      </c>
+      <c r="E135" t="s">
         <v>23</v>
-      </c>
-      <c r="E135" t="s">
-        <v>31</v>
       </c>
       <c r="F135">
         <v>120.7</v>
@@ -4377,27 +4377,27 @@
         <v>25.3</v>
       </c>
       <c r="H135" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I135" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B136">
         <v>11</v>
       </c>
       <c r="C136" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D136" t="s">
+        <v>15</v>
+      </c>
+      <c r="E136" t="s">
         <v>23</v>
-      </c>
-      <c r="E136" t="s">
-        <v>31</v>
       </c>
       <c r="F136">
         <v>143.6</v>
@@ -4406,27 +4406,27 @@
         <v>40.700000000000003</v>
       </c>
       <c r="H136" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I136" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B137">
         <v>8</v>
       </c>
       <c r="C137" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D137" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E137" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F137">
         <v>127.7</v>
@@ -4435,27 +4435,27 @@
         <v>24.4</v>
       </c>
       <c r="H137" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I137" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B138">
         <v>10</v>
       </c>
       <c r="C138" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D138" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E138" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F138">
         <v>131.9</v>
@@ -4464,27 +4464,27 @@
         <v>25.5</v>
       </c>
       <c r="H138" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I138" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B139">
         <v>10</v>
       </c>
       <c r="C139" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D139" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E139" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F139">
         <v>139.6</v>
@@ -4493,27 +4493,27 @@
         <v>32.299999999999997</v>
       </c>
       <c r="H139" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I139" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B140">
         <v>9</v>
       </c>
       <c r="C140" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D140" t="s">
+        <v>15</v>
+      </c>
+      <c r="E140" t="s">
         <v>23</v>
-      </c>
-      <c r="E140" t="s">
-        <v>31</v>
       </c>
       <c r="F140">
         <v>137</v>
@@ -4522,27 +4522,27 @@
         <v>42.3</v>
       </c>
       <c r="H140" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I140" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B141">
         <v>10</v>
       </c>
       <c r="C141" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D141" t="s">
+        <v>15</v>
+      </c>
+      <c r="E141" t="s">
         <v>23</v>
-      </c>
-      <c r="E141" t="s">
-        <v>31</v>
       </c>
       <c r="F141">
         <v>137</v>
@@ -4551,27 +4551,27 @@
         <v>43.9</v>
       </c>
       <c r="H141" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I141" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B142">
         <v>11</v>
       </c>
       <c r="C142" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D142" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E142" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F142">
         <v>143.30000000000001</v>
@@ -4580,27 +4580,27 @@
         <v>33.4</v>
       </c>
       <c r="H142" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I142" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B143">
         <v>9</v>
       </c>
       <c r="C143" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D143" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E143" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F143">
         <v>129.4</v>
@@ -4609,27 +4609,27 @@
         <v>25.8</v>
       </c>
       <c r="H143" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I143" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B144">
         <v>10</v>
       </c>
       <c r="C144" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D144" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E144" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F144">
         <v>127.2</v>
@@ -4638,27 +4638,27 @@
         <v>21.7</v>
       </c>
       <c r="H144" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I144" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B145">
         <v>11</v>
       </c>
       <c r="C145" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D145" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E145" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F145">
         <v>145.19999999999999</v>
@@ -4667,27 +4667,27 @@
         <v>34.799999999999997</v>
       </c>
       <c r="H145" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I145" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B146">
         <v>11</v>
       </c>
       <c r="C146" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D146" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E146" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F146">
         <v>140.4</v>
@@ -4696,27 +4696,27 @@
         <v>29.8</v>
       </c>
       <c r="H146" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I146" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B147">
         <v>7</v>
       </c>
       <c r="C147" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D147" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E147" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F147">
         <v>146.6</v>
@@ -4725,27 +4725,27 @@
         <v>35.1</v>
       </c>
       <c r="H147" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I147" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B148">
         <v>6</v>
       </c>
       <c r="C148" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D148" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E148" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F148">
         <v>135.5</v>
@@ -4754,27 +4754,27 @@
         <v>29.1</v>
       </c>
       <c r="H148" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I148" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B149">
         <v>8</v>
       </c>
       <c r="C149" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D149" t="s">
+        <v>15</v>
+      </c>
+      <c r="E149" t="s">
         <v>23</v>
-      </c>
-      <c r="E149" t="s">
-        <v>31</v>
       </c>
       <c r="F149">
         <v>125.7</v>
@@ -4783,27 +4783,27 @@
         <v>27.8</v>
       </c>
       <c r="H149" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I149" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B150">
         <v>10</v>
       </c>
       <c r="C150" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D150" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E150" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F150">
         <v>137.4</v>
@@ -4812,27 +4812,27 @@
         <v>30.9</v>
       </c>
       <c r="H150" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I150" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B151">
         <v>11</v>
       </c>
       <c r="C151" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D151" t="s">
+        <v>15</v>
+      </c>
+      <c r="E151" t="s">
         <v>23</v>
-      </c>
-      <c r="E151" t="s">
-        <v>31</v>
       </c>
       <c r="F151">
         <v>153.19999999999999</v>
@@ -4841,27 +4841,27 @@
         <v>48.2</v>
       </c>
       <c r="H151" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I151" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B152">
         <v>11</v>
       </c>
       <c r="C152" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D152" t="s">
+        <v>15</v>
+      </c>
+      <c r="E152" t="s">
         <v>23</v>
-      </c>
-      <c r="E152" t="s">
-        <v>31</v>
       </c>
       <c r="F152">
         <v>149.19999999999999</v>
@@ -4870,27 +4870,27 @@
         <v>42.8</v>
       </c>
       <c r="H152" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I152" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B153">
         <v>10</v>
       </c>
       <c r="C153" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D153" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E153" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F153">
         <v>141.30000000000001</v>
@@ -4899,27 +4899,27 @@
         <v>30.7</v>
       </c>
       <c r="H153" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I153" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B154">
         <v>5</v>
       </c>
       <c r="C154" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D154" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E154" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F154">
         <v>139.6</v>
@@ -4928,27 +4928,27 @@
         <v>28.5</v>
       </c>
       <c r="H154" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I154" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B155">
         <v>6</v>
       </c>
       <c r="C155" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D155" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E155" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F155">
         <v>134.19999999999999</v>
@@ -4957,27 +4957,27 @@
         <v>32.200000000000003</v>
       </c>
       <c r="H155" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I155" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B156">
         <v>11</v>
       </c>
       <c r="C156" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D156" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E156" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F156">
         <v>146.80000000000001</v>
@@ -4986,27 +4986,27 @@
         <v>32.9</v>
       </c>
       <c r="H156" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I156" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B157">
         <v>11</v>
       </c>
       <c r="C157" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D157" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E157" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F157">
         <v>146.80000000000001</v>
@@ -5015,27 +5015,27 @@
         <v>35.5</v>
       </c>
       <c r="H157" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I157" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B158">
         <v>11</v>
       </c>
       <c r="C158" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D158" t="s">
+        <v>15</v>
+      </c>
+      <c r="E158" t="s">
         <v>23</v>
-      </c>
-      <c r="E158" t="s">
-        <v>31</v>
       </c>
       <c r="F158">
         <v>144</v>
@@ -5044,27 +5044,27 @@
         <v>41.8</v>
       </c>
       <c r="H158" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I158" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B159">
         <v>6</v>
       </c>
       <c r="C159" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D159" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E159" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F159">
         <v>140</v>
@@ -5073,27 +5073,27 @@
         <v>28.8</v>
       </c>
       <c r="H159" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I159" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B160">
         <v>7</v>
       </c>
       <c r="C160" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D160" t="s">
+        <v>15</v>
+      </c>
+      <c r="E160" t="s">
         <v>23</v>
-      </c>
-      <c r="E160" t="s">
-        <v>31</v>
       </c>
       <c r="F160">
         <v>132.19999999999999</v>
@@ -5102,27 +5102,27 @@
         <v>34.799999999999997</v>
       </c>
       <c r="H160" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I160" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B161">
         <v>8</v>
       </c>
       <c r="C161" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D161" t="s">
+        <v>15</v>
+      </c>
+      <c r="E161" t="s">
         <v>23</v>
-      </c>
-      <c r="E161" t="s">
-        <v>31</v>
       </c>
       <c r="F161">
         <v>132.5</v>
@@ -5131,27 +5131,27 @@
         <v>35.299999999999997</v>
       </c>
       <c r="H161" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I161" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B162">
         <v>5</v>
       </c>
       <c r="C162" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D162" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E162" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F162">
         <v>147</v>
@@ -5160,27 +5160,27 @@
         <v>31.7</v>
       </c>
       <c r="H162" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I162" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B163">
         <v>9</v>
       </c>
       <c r="C163" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D163" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E163" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F163">
         <v>135.80000000000001</v>
@@ -5189,27 +5189,27 @@
         <v>26.5</v>
       </c>
       <c r="H163" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I163" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B164">
         <v>5</v>
       </c>
       <c r="C164" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D164" t="s">
+        <v>15</v>
+      </c>
+      <c r="E164" t="s">
         <v>23</v>
-      </c>
-      <c r="E164" t="s">
-        <v>31</v>
       </c>
       <c r="F164">
         <v>146.1</v>
@@ -5218,27 +5218,27 @@
         <v>41.6</v>
       </c>
       <c r="H164" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I164" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B165">
         <v>9</v>
       </c>
       <c r="C165" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D165" t="s">
+        <v>15</v>
+      </c>
+      <c r="E165" t="s">
         <v>23</v>
-      </c>
-      <c r="E165" t="s">
-        <v>31</v>
       </c>
       <c r="F165">
         <v>126.3</v>
@@ -5247,27 +5247,27 @@
         <v>32.700000000000003</v>
       </c>
       <c r="H165" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I165" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B166">
         <v>10</v>
       </c>
       <c r="C166" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D166" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E166" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F166">
         <v>141.19999999999999</v>
@@ -5276,27 +5276,27 @@
         <v>29.5</v>
       </c>
       <c r="H166" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I166" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B167">
         <v>11</v>
       </c>
       <c r="C167" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D167" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E167" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F167">
         <v>145.5</v>
@@ -5305,27 +5305,27 @@
         <v>28</v>
       </c>
       <c r="H167" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I167" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B168">
         <v>11</v>
       </c>
       <c r="C168" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D168" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E168" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F168">
         <v>144.6</v>
@@ -5334,27 +5334,27 @@
         <v>30.2</v>
       </c>
       <c r="H168" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I168" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B169">
         <v>6</v>
       </c>
       <c r="C169" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D169" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E169" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F169">
         <v>144.9</v>
@@ -5363,27 +5363,27 @@
         <v>31.8</v>
       </c>
       <c r="H169" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I169" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B170">
         <v>9</v>
       </c>
       <c r="C170" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D170" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E170" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F170">
         <v>133.6</v>
@@ -5392,27 +5392,27 @@
         <v>31</v>
       </c>
       <c r="H170" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I170" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B171">
         <v>9</v>
       </c>
       <c r="C171" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D171" t="s">
+        <v>15</v>
+      </c>
+      <c r="E171" t="s">
         <v>23</v>
-      </c>
-      <c r="E171" t="s">
-        <v>31</v>
       </c>
       <c r="F171">
         <v>127.9</v>
@@ -5421,27 +5421,27 @@
         <v>31.2</v>
       </c>
       <c r="H171" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I171" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B172">
         <v>9</v>
       </c>
       <c r="C172" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D172" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E172" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F172">
         <v>133</v>
@@ -5450,27 +5450,27 @@
         <v>27.1</v>
       </c>
       <c r="H172" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I172" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B173">
         <v>11</v>
       </c>
       <c r="C173" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D173" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E173" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F173">
         <v>147.19999999999999</v>
@@ -5479,27 +5479,27 @@
         <v>36.6</v>
       </c>
       <c r="H173" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I173" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B174">
         <v>8</v>
       </c>
       <c r="C174" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D174" t="s">
+        <v>15</v>
+      </c>
+      <c r="E174" t="s">
         <v>23</v>
-      </c>
-      <c r="E174" t="s">
-        <v>31</v>
       </c>
       <c r="F174">
         <v>121.3</v>
@@ -5508,27 +5508,27 @@
         <v>29.4</v>
       </c>
       <c r="H174" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I174" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B175">
         <v>10</v>
       </c>
       <c r="C175" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D175" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E175" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F175">
         <v>142</v>
@@ -5537,27 +5537,27 @@
         <v>32.6</v>
       </c>
       <c r="H175" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I175" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B176">
         <v>6</v>
       </c>
       <c r="C176" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D176" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E176" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F176">
         <v>134.80000000000001</v>
@@ -5566,27 +5566,27 @@
         <v>28.5</v>
       </c>
       <c r="H176" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I176" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B177">
         <v>11</v>
       </c>
       <c r="C177" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D177" t="s">
+        <v>15</v>
+      </c>
+      <c r="E177" t="s">
         <v>23</v>
-      </c>
-      <c r="E177" t="s">
-        <v>31</v>
       </c>
       <c r="F177">
         <v>150.19999999999999</v>
@@ -5595,27 +5595,27 @@
         <v>44.4</v>
       </c>
       <c r="H177" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I177" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B178">
         <v>11</v>
       </c>
       <c r="C178" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D178" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E178" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F178">
         <v>146.30000000000001</v>
@@ -5624,27 +5624,27 @@
         <v>29.2</v>
       </c>
       <c r="H178" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I178" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B179">
         <v>10</v>
       </c>
       <c r="C179" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D179" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E179" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F179">
         <v>141.1</v>
@@ -5653,27 +5653,27 @@
         <v>32.299999999999997</v>
       </c>
       <c r="H179" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I179" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B180">
         <v>10</v>
       </c>
       <c r="C180" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D180" t="s">
+        <v>15</v>
+      </c>
+      <c r="E180" t="s">
         <v>23</v>
-      </c>
-      <c r="E180" t="s">
-        <v>31</v>
       </c>
       <c r="F180">
         <v>141.80000000000001</v>
@@ -5682,27 +5682,27 @@
         <v>44.5</v>
       </c>
       <c r="H180" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I180" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B181">
         <v>11</v>
       </c>
       <c r="C181" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D181" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E181" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F181">
         <v>148.1</v>
@@ -5711,27 +5711,27 @@
         <v>38</v>
       </c>
       <c r="H181" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I181" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B182">
         <v>11</v>
       </c>
       <c r="C182" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D182" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E182" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F182">
         <v>143.4</v>
@@ -5740,27 +5740,27 @@
         <v>33.1</v>
       </c>
       <c r="H182" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I182" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B183">
         <v>6</v>
       </c>
       <c r="C183" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D183" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E183" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F183">
         <v>133.30000000000001</v>
@@ -5769,27 +5769,27 @@
         <v>27.9</v>
       </c>
       <c r="H183" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I183" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B184">
         <v>10</v>
       </c>
       <c r="C184" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D184" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E184" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F184">
         <v>133.1</v>
@@ -5798,27 +5798,27 @@
         <v>30.1</v>
       </c>
       <c r="H184" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I184" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B185">
         <v>12</v>
       </c>
       <c r="C185" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D185" t="s">
+        <v>15</v>
+      </c>
+      <c r="E185" t="s">
         <v>23</v>
-      </c>
-      <c r="E185" t="s">
-        <v>31</v>
       </c>
       <c r="F185">
         <v>143.80000000000001</v>
@@ -5827,27 +5827,27 @@
         <v>43.5</v>
       </c>
       <c r="H185" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I185" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B186">
         <v>8</v>
       </c>
       <c r="C186" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D186" t="s">
+        <v>15</v>
+      </c>
+      <c r="E186" t="s">
         <v>23</v>
-      </c>
-      <c r="E186" t="s">
-        <v>31</v>
       </c>
       <c r="F186">
         <v>137.4</v>
@@ -5856,27 +5856,27 @@
         <v>40.799999999999997</v>
       </c>
       <c r="H186" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I186" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B187">
         <v>11</v>
       </c>
       <c r="C187" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D187" t="s">
+        <v>15</v>
+      </c>
+      <c r="E187" t="s">
         <v>23</v>
-      </c>
-      <c r="E187" t="s">
-        <v>31</v>
       </c>
       <c r="F187">
         <v>136.30000000000001</v>
@@ -5885,27 +5885,27 @@
         <v>36.200000000000003</v>
       </c>
       <c r="H187" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I187" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B188">
         <v>12</v>
       </c>
       <c r="C188" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D188" t="s">
+        <v>15</v>
+      </c>
+      <c r="E188" t="s">
         <v>23</v>
-      </c>
-      <c r="E188" t="s">
-        <v>31</v>
       </c>
       <c r="F188">
         <v>143.6</v>
@@ -5914,27 +5914,27 @@
         <v>38.4</v>
       </c>
       <c r="H188" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I188" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B189">
         <v>11</v>
       </c>
       <c r="C189" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D189" t="s">
+        <v>15</v>
+      </c>
+      <c r="E189" t="s">
         <v>23</v>
-      </c>
-      <c r="E189" t="s">
-        <v>31</v>
       </c>
       <c r="F189">
         <v>142.69999999999999</v>
@@ -5943,27 +5943,27 @@
         <v>40.799999999999997</v>
       </c>
       <c r="H189" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I189" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B190">
         <v>6</v>
       </c>
       <c r="C190" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D190" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E190" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F190">
         <v>135.69999999999999</v>
@@ -5972,27 +5972,27 @@
         <v>28.9</v>
       </c>
       <c r="H190" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I190" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B191">
         <v>10</v>
       </c>
       <c r="C191" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D191" t="s">
+        <v>15</v>
+      </c>
+      <c r="E191" t="s">
         <v>23</v>
-      </c>
-      <c r="E191" t="s">
-        <v>31</v>
       </c>
       <c r="F191">
         <v>134.19999999999999</v>
@@ -6001,27 +6001,27 @@
         <v>37.299999999999997</v>
       </c>
       <c r="H191" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I191" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B192">
         <v>10</v>
       </c>
       <c r="C192" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D192" t="s">
+        <v>15</v>
+      </c>
+      <c r="E192" t="s">
         <v>23</v>
-      </c>
-      <c r="E192" t="s">
-        <v>31</v>
       </c>
       <c r="F192">
         <v>137.19999999999999</v>
@@ -6030,27 +6030,27 @@
         <v>35.1</v>
       </c>
       <c r="H192" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I192" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B193">
         <v>9</v>
       </c>
       <c r="C193" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D193" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E193" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F193">
         <v>130.1</v>
@@ -6059,27 +6059,27 @@
         <v>28.2</v>
       </c>
       <c r="H193" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I193" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B194">
         <v>7</v>
       </c>
       <c r="C194" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D194" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E194" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F194">
         <v>134.6</v>
@@ -6088,27 +6088,27 @@
         <v>30.2</v>
       </c>
       <c r="H194" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I194" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B195">
         <v>11</v>
       </c>
       <c r="C195" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D195" t="s">
+        <v>15</v>
+      </c>
+      <c r="E195" t="s">
         <v>23</v>
-      </c>
-      <c r="E195" t="s">
-        <v>31</v>
       </c>
       <c r="F195">
         <v>147.6</v>
@@ -6117,27 +6117,27 @@
         <v>44.4</v>
       </c>
       <c r="H195" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I195" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B196">
         <v>7</v>
       </c>
       <c r="C196" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D196" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E196" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F196">
         <v>145</v>
@@ -6146,27 +6146,27 @@
         <v>23.9</v>
       </c>
       <c r="H196" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I196" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B197">
         <v>11</v>
       </c>
       <c r="C197" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D197" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E197" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F197">
         <v>149.69999999999999</v>
@@ -6175,27 +6175,27 @@
         <v>36.200000000000003</v>
       </c>
       <c r="H197" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I197" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B198">
         <v>11</v>
       </c>
       <c r="C198" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D198" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E198" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F198">
         <v>142</v>
@@ -6204,27 +6204,27 @@
         <v>35.799999999999997</v>
       </c>
       <c r="H198" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I198" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B199">
         <v>7</v>
       </c>
       <c r="C199" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D199" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E199" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F199">
         <v>142.1</v>
@@ -6233,27 +6233,27 @@
         <v>24.8</v>
       </c>
       <c r="H199" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I199" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B200">
         <v>9</v>
       </c>
       <c r="C200" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D200" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E200" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F200">
         <v>126</v>
@@ -6262,27 +6262,27 @@
         <v>26</v>
       </c>
       <c r="H200" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I200" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B201">
         <v>0</v>
       </c>
       <c r="C201" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D201" t="s">
+        <v>15</v>
+      </c>
+      <c r="E201" t="s">
         <v>23</v>
-      </c>
-      <c r="E201" t="s">
-        <v>31</v>
       </c>
       <c r="F201">
         <v>134.80000000000001</v>
@@ -6291,27 +6291,27 @@
         <v>33.700000000000003</v>
       </c>
       <c r="H201" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I201" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B202">
         <v>10</v>
       </c>
       <c r="C202" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D202" t="s">
+        <v>15</v>
+      </c>
+      <c r="E202" t="s">
         <v>23</v>
-      </c>
-      <c r="E202" t="s">
-        <v>31</v>
       </c>
       <c r="F202">
         <v>134.80000000000001</v>
@@ -6320,27 +6320,27 @@
         <v>35.4</v>
       </c>
       <c r="H202" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I202" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B203">
         <v>11</v>
       </c>
       <c r="C203" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D203" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E203" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F203">
         <v>133.4</v>
@@ -6349,27 +6349,27 @@
         <v>30.4</v>
       </c>
       <c r="H203" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I203" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B204">
         <v>11</v>
       </c>
       <c r="C204" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D204" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E204" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F204">
         <v>144.9</v>
@@ -6378,27 +6378,27 @@
         <v>30.1</v>
       </c>
       <c r="H204" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I204" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B205">
         <v>11</v>
       </c>
       <c r="C205" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D205" t="s">
+        <v>15</v>
+      </c>
+      <c r="E205" t="s">
         <v>23</v>
-      </c>
-      <c r="E205" t="s">
-        <v>31</v>
       </c>
       <c r="F205">
         <v>149.19999999999999</v>
@@ -6407,27 +6407,27 @@
         <v>45.2</v>
       </c>
       <c r="H205" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I205" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B206">
         <v>12</v>
       </c>
       <c r="C206" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D206" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E206" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F206">
         <v>141</v>
@@ -6436,27 +6436,27 @@
         <v>32.299999999999997</v>
       </c>
       <c r="H206" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I206" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B207">
         <v>12</v>
       </c>
       <c r="C207" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D207" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E207" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F207">
         <v>147.5</v>
@@ -6465,27 +6465,27 @@
         <v>33.9</v>
       </c>
       <c r="H207" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I207" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B208">
         <v>12</v>
       </c>
       <c r="C208" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D208" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E208" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F208">
         <v>142.30000000000001</v>
@@ -6494,27 +6494,27 @@
         <v>28.9</v>
       </c>
       <c r="H208" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I208" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B209">
         <v>9</v>
       </c>
       <c r="C209" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D209" t="s">
+        <v>15</v>
+      </c>
+      <c r="E209" t="s">
         <v>23</v>
-      </c>
-      <c r="E209" t="s">
-        <v>31</v>
       </c>
       <c r="F209">
         <v>132.30000000000001</v>
@@ -6523,27 +6523,27 @@
         <v>33.4</v>
       </c>
       <c r="H209" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I209" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B210">
         <v>9</v>
       </c>
       <c r="C210" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D210" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E210" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F210">
         <v>132.19999999999999</v>
@@ -6552,27 +6552,27 @@
         <v>29.4</v>
       </c>
       <c r="H210" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I210" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B211">
         <v>10</v>
       </c>
       <c r="C211" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D211" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E211" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F211">
         <v>139.1</v>
@@ -6581,27 +6581,27 @@
         <v>31.1</v>
       </c>
       <c r="H211" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I211" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B212">
         <v>11</v>
       </c>
       <c r="C212" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D212" t="s">
+        <v>15</v>
+      </c>
+      <c r="E212" t="s">
         <v>23</v>
-      </c>
-      <c r="E212" t="s">
-        <v>31</v>
       </c>
       <c r="F212">
         <v>137.9</v>
@@ -6610,27 +6610,27 @@
         <v>44.5</v>
       </c>
       <c r="H212" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I212" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B213">
         <v>9</v>
       </c>
       <c r="C213" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D213" t="s">
+        <v>15</v>
+      </c>
+      <c r="E213" t="s">
         <v>23</v>
-      </c>
-      <c r="E213" t="s">
-        <v>31</v>
       </c>
       <c r="F213">
         <v>134.6</v>
@@ -6639,27 +6639,27 @@
         <v>41.8</v>
       </c>
       <c r="H213" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I213" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B214">
         <v>10</v>
       </c>
       <c r="C214" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D214" t="s">
+        <v>15</v>
+      </c>
+      <c r="E214" t="s">
         <v>23</v>
-      </c>
-      <c r="E214" t="s">
-        <v>31</v>
       </c>
       <c r="F214">
         <v>134.30000000000001</v>
@@ -6668,10 +6668,10 @@
         <v>34.799999999999997</v>
       </c>
       <c r="H214" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I214" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6687,27 +6687,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/datadescrip/datos_actfisica_flexibilidad.xlsx
+++ b/datadescrip/datos_actfisica_flexibilidad.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Datos\datadescrip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2BD95BB-DA10-4E40-B9AE-76DD1760F452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62EE43B5-7FD2-4C64-8D49-BBF82EA0A114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="32">
   <si>
     <t>Flexibilidad</t>
   </si>
@@ -57,9 +57,6 @@
   </si>
   <si>
     <t xml:space="preserve">Muy baja </t>
-  </si>
-  <si>
-    <t>bajo</t>
   </si>
   <si>
     <t>Segundo</t>
@@ -462,42 +459,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I214"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="15.44140625" customWidth="1"/>
+    <col min="9" max="9" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" t="s">
-        <v>29</v>
-      </c>
       <c r="F1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H1" t="s">
         <v>0</v>
       </c>
       <c r="I1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -511,7 +510,7 @@
         <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>114.3</v>
@@ -540,7 +539,7 @@
         <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F3">
         <v>114.4</v>
@@ -555,7 +554,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -569,7 +568,7 @@
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F4">
         <v>114.4</v>
@@ -584,7 +583,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -598,7 +597,7 @@
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F5">
         <v>122.7</v>
@@ -613,7 +612,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -627,7 +626,7 @@
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F6">
         <v>113.9</v>
@@ -642,7 +641,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -656,7 +655,7 @@
         <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F7">
         <v>127.2</v>
@@ -671,7 +670,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -685,7 +684,7 @@
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F8">
         <v>118.3</v>
@@ -700,7 +699,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -714,7 +713,7 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F9">
         <v>111.3</v>
@@ -729,7 +728,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -743,7 +742,7 @@
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F10">
         <v>116.2</v>
@@ -758,7 +757,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -772,7 +771,7 @@
         <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F11">
         <v>116.2</v>
@@ -787,7 +786,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>1</v>
       </c>
@@ -801,7 +800,7 @@
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F12">
         <v>134.69999999999999</v>
@@ -816,7 +815,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -830,7 +829,7 @@
         <v>3</v>
       </c>
       <c r="E13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F13">
         <v>114.4</v>
@@ -845,7 +844,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -859,7 +858,7 @@
         <v>3</v>
       </c>
       <c r="E14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F14">
         <v>120.4</v>
@@ -888,7 +887,7 @@
         <v>3</v>
       </c>
       <c r="E15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F15">
         <v>122.9</v>
@@ -903,7 +902,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -917,7 +916,7 @@
         <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F16">
         <v>118.9</v>
@@ -932,7 +931,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -946,7 +945,7 @@
         <v>3</v>
       </c>
       <c r="E17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F17">
         <v>117.8</v>
@@ -961,7 +960,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -975,7 +974,7 @@
         <v>3</v>
       </c>
       <c r="E18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F18">
         <v>102.9</v>
@@ -990,7 +989,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>1</v>
       </c>
@@ -1004,7 +1003,7 @@
         <v>3</v>
       </c>
       <c r="E19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F19">
         <v>110.4</v>
@@ -1019,7 +1018,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>1</v>
       </c>
@@ -1033,7 +1032,7 @@
         <v>3</v>
       </c>
       <c r="E20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F20">
         <v>118.3</v>
@@ -1062,7 +1061,7 @@
         <v>3</v>
       </c>
       <c r="E21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F21">
         <v>119.2</v>
@@ -1074,10 +1073,10 @@
         <v>10</v>
       </c>
       <c r="I21" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>1</v>
       </c>
@@ -1091,7 +1090,7 @@
         <v>3</v>
       </c>
       <c r="E22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F22">
         <v>115.6</v>
@@ -1106,7 +1105,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>1</v>
       </c>
@@ -1120,7 +1119,7 @@
         <v>3</v>
       </c>
       <c r="E23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F23">
         <v>115.6</v>
@@ -1135,7 +1134,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>1</v>
       </c>
@@ -1149,7 +1148,7 @@
         <v>3</v>
       </c>
       <c r="E24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F24">
         <v>118.2</v>
@@ -1164,7 +1163,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>1</v>
       </c>
@@ -1178,7 +1177,7 @@
         <v>3</v>
       </c>
       <c r="E25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F25">
         <v>118.2</v>
@@ -1193,7 +1192,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>1</v>
       </c>
@@ -1207,7 +1206,7 @@
         <v>3</v>
       </c>
       <c r="E26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F26">
         <v>112.9</v>
@@ -1222,7 +1221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>1</v>
       </c>
@@ -1236,7 +1235,7 @@
         <v>3</v>
       </c>
       <c r="E27" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F27">
         <v>113.7</v>
@@ -1265,7 +1264,7 @@
         <v>3</v>
       </c>
       <c r="E28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F28">
         <v>114.7</v>
@@ -1280,7 +1279,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>1</v>
       </c>
@@ -1294,7 +1293,7 @@
         <v>3</v>
       </c>
       <c r="E29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F29">
         <v>111.9</v>
@@ -1323,7 +1322,7 @@
         <v>3</v>
       </c>
       <c r="E30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F30">
         <v>135.80000000000001</v>
@@ -1338,7 +1337,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>1</v>
       </c>
@@ -1352,7 +1351,7 @@
         <v>3</v>
       </c>
       <c r="E31" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F31">
         <v>117.5</v>
@@ -1367,7 +1366,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>1</v>
       </c>
@@ -1381,7 +1380,7 @@
         <v>3</v>
       </c>
       <c r="E32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F32">
         <v>133.1</v>
@@ -1396,7 +1395,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>1</v>
       </c>
@@ -1410,7 +1409,7 @@
         <v>3</v>
       </c>
       <c r="E33" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F33">
         <v>108.9</v>
@@ -1425,7 +1424,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>1</v>
       </c>
@@ -1439,7 +1438,7 @@
         <v>3</v>
       </c>
       <c r="E34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F34">
         <v>131.80000000000001</v>
@@ -1454,7 +1453,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>1</v>
       </c>
@@ -1468,7 +1467,7 @@
         <v>3</v>
       </c>
       <c r="E35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F35">
         <v>122.2</v>
@@ -1497,7 +1496,7 @@
         <v>3</v>
       </c>
       <c r="E36" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F36">
         <v>114.4</v>
@@ -1512,7 +1511,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>1</v>
       </c>
@@ -1526,7 +1525,7 @@
         <v>3</v>
       </c>
       <c r="E37" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F37">
         <v>118.9</v>
@@ -1555,7 +1554,7 @@
         <v>3</v>
       </c>
       <c r="E38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F38">
         <v>118.1</v>
@@ -1584,7 +1583,7 @@
         <v>3</v>
       </c>
       <c r="E39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F39">
         <v>112.2</v>
@@ -1599,7 +1598,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>1</v>
       </c>
@@ -1613,7 +1612,7 @@
         <v>3</v>
       </c>
       <c r="E40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F40">
         <v>120.8</v>
@@ -1628,7 +1627,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>1</v>
       </c>
@@ -1642,7 +1641,7 @@
         <v>3</v>
       </c>
       <c r="E41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F41">
         <v>115.6</v>
@@ -1657,7 +1656,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>1</v>
       </c>
@@ -1671,7 +1670,7 @@
         <v>3</v>
       </c>
       <c r="E42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F42">
         <v>111.4</v>
@@ -1700,7 +1699,7 @@
         <v>3</v>
       </c>
       <c r="E43" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F43">
         <v>106.8</v>
@@ -1729,7 +1728,7 @@
         <v>3</v>
       </c>
       <c r="E44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F44">
         <v>112.2</v>
@@ -1744,7 +1743,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>1</v>
       </c>
@@ -1758,7 +1757,7 @@
         <v>3</v>
       </c>
       <c r="E45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F45">
         <v>133</v>
@@ -1787,7 +1786,7 @@
         <v>3</v>
       </c>
       <c r="E46" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F46">
         <v>134.30000000000001</v>
@@ -1802,7 +1801,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>1</v>
       </c>
@@ -1816,7 +1815,7 @@
         <v>3</v>
       </c>
       <c r="E47" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F47">
         <v>132.4</v>
@@ -1845,7 +1844,7 @@
         <v>3</v>
       </c>
       <c r="E48" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F48">
         <v>117.4</v>
@@ -1874,7 +1873,7 @@
         <v>3</v>
       </c>
       <c r="E49" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F49">
         <v>119.5</v>
@@ -1903,7 +1902,7 @@
         <v>3</v>
       </c>
       <c r="E50" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F50">
         <v>121.1</v>
@@ -1918,7 +1917,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>1</v>
       </c>
@@ -1932,7 +1931,7 @@
         <v>3</v>
       </c>
       <c r="E51" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F51">
         <v>124.8</v>
@@ -1961,7 +1960,7 @@
         <v>3</v>
       </c>
       <c r="E52" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F52">
         <v>123</v>
@@ -1976,7 +1975,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>1</v>
       </c>
@@ -1990,7 +1989,7 @@
         <v>3</v>
       </c>
       <c r="E53" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F53">
         <v>113.4</v>
@@ -2005,7 +2004,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>1</v>
       </c>
@@ -2019,7 +2018,7 @@
         <v>3</v>
       </c>
       <c r="E54" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F54">
         <v>132.19999999999999</v>
@@ -2034,7 +2033,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>1</v>
       </c>
@@ -2048,7 +2047,7 @@
         <v>3</v>
       </c>
       <c r="E55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F55">
         <v>120.1</v>
@@ -2063,7 +2062,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>1</v>
       </c>
@@ -2077,7 +2076,7 @@
         <v>3</v>
       </c>
       <c r="E56" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F56">
         <v>109.1</v>
@@ -2106,7 +2105,7 @@
         <v>3</v>
       </c>
       <c r="E57" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F57">
         <v>135.80000000000001</v>
@@ -2135,7 +2134,7 @@
         <v>3</v>
       </c>
       <c r="E58" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F58">
         <v>118.9</v>
@@ -2150,7 +2149,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>1</v>
       </c>
@@ -2164,7 +2163,7 @@
         <v>3</v>
       </c>
       <c r="E59" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F59">
         <v>123.6</v>
@@ -2179,7 +2178,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>1</v>
       </c>
@@ -2193,7 +2192,7 @@
         <v>3</v>
       </c>
       <c r="E60" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F60">
         <v>112.9</v>
@@ -2208,7 +2207,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>1</v>
       </c>
@@ -2222,7 +2221,7 @@
         <v>3</v>
       </c>
       <c r="E61" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F61">
         <v>112.8</v>
@@ -2251,7 +2250,7 @@
         <v>3</v>
       </c>
       <c r="E62" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F62">
         <v>126.5</v>
@@ -2266,7 +2265,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>1</v>
       </c>
@@ -2280,7 +2279,7 @@
         <v>3</v>
       </c>
       <c r="E63" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F63">
         <v>128.1</v>
@@ -2295,7 +2294,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>1</v>
       </c>
@@ -2309,7 +2308,7 @@
         <v>3</v>
       </c>
       <c r="E64" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F64">
         <v>120.4</v>
@@ -2324,7 +2323,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>1</v>
       </c>
@@ -2338,7 +2337,7 @@
         <v>3</v>
       </c>
       <c r="E65" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F65">
         <v>126.4</v>
@@ -2353,7 +2352,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>1</v>
       </c>
@@ -2367,7 +2366,7 @@
         <v>3</v>
       </c>
       <c r="E66" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F66">
         <v>122.8</v>
@@ -2382,7 +2381,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>1</v>
       </c>
@@ -2396,7 +2395,7 @@
         <v>3</v>
       </c>
       <c r="E67" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F67">
         <v>114.4</v>
@@ -2411,7 +2410,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>1</v>
       </c>
@@ -2425,7 +2424,7 @@
         <v>3</v>
       </c>
       <c r="E68" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F68">
         <v>124.7</v>
@@ -2440,7 +2439,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>1</v>
       </c>
@@ -2454,7 +2453,7 @@
         <v>3</v>
       </c>
       <c r="E69" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F69">
         <v>138</v>
@@ -2483,7 +2482,7 @@
         <v>3</v>
       </c>
       <c r="E70" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F70">
         <v>123.7</v>
@@ -2498,7 +2497,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>1</v>
       </c>
@@ -2512,7 +2511,7 @@
         <v>3</v>
       </c>
       <c r="E71" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F71">
         <v>115.3</v>
@@ -2541,7 +2540,7 @@
         <v>3</v>
       </c>
       <c r="E72" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F72">
         <v>119.8</v>
@@ -2556,7 +2555,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>1</v>
       </c>
@@ -2570,7 +2569,7 @@
         <v>3</v>
       </c>
       <c r="E73" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F73">
         <v>126</v>
@@ -2585,7 +2584,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>1</v>
       </c>
@@ -2599,7 +2598,7 @@
         <v>3</v>
       </c>
       <c r="E74" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F74">
         <v>112.9</v>
@@ -2614,7 +2613,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>1</v>
       </c>
@@ -2628,7 +2627,7 @@
         <v>3</v>
       </c>
       <c r="E75" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F75">
         <v>108.2</v>
@@ -2643,7 +2642,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>1</v>
       </c>
@@ -2657,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="E76" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F76">
         <v>117.3</v>
@@ -2672,7 +2671,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>1</v>
       </c>
@@ -2686,7 +2685,7 @@
         <v>3</v>
       </c>
       <c r="E77" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F77">
         <v>140.19999999999999</v>
@@ -2701,7 +2700,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>1</v>
       </c>
@@ -2715,7 +2714,7 @@
         <v>3</v>
       </c>
       <c r="E78" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F78">
         <v>126.4</v>
@@ -2730,7 +2729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>1</v>
       </c>
@@ -2744,7 +2743,7 @@
         <v>3</v>
       </c>
       <c r="E79" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F79">
         <v>118.6</v>
@@ -2759,7 +2758,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>1</v>
       </c>
@@ -2770,10 +2769,10 @@
         <v>9</v>
       </c>
       <c r="D80" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E80" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F80">
         <v>123.5</v>
@@ -2788,7 +2787,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>1</v>
       </c>
@@ -2799,10 +2798,10 @@
         <v>9</v>
       </c>
       <c r="D81" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E81" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F81">
         <v>116.4</v>
@@ -2817,7 +2816,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>1</v>
       </c>
@@ -2828,10 +2827,10 @@
         <v>9</v>
       </c>
       <c r="D82" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E82" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F82">
         <v>144.4</v>
@@ -2857,10 +2856,10 @@
         <v>9</v>
       </c>
       <c r="D83" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E83" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F83">
         <v>134.4</v>
@@ -2886,10 +2885,10 @@
         <v>9</v>
       </c>
       <c r="D84" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E84" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F84">
         <v>117.2</v>
@@ -2904,7 +2903,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>1</v>
       </c>
@@ -2915,10 +2914,10 @@
         <v>9</v>
       </c>
       <c r="D85" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E85" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F85">
         <v>138.6</v>
@@ -2927,13 +2926,13 @@
         <v>45.1</v>
       </c>
       <c r="H85" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I85" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>1</v>
       </c>
@@ -2944,10 +2943,10 @@
         <v>9</v>
       </c>
       <c r="D86" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E86" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F86">
         <v>122.6</v>
@@ -2962,7 +2961,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>1</v>
       </c>
@@ -2973,10 +2972,10 @@
         <v>2</v>
       </c>
       <c r="D87" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E87" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F87">
         <v>138</v>
@@ -3002,10 +3001,10 @@
         <v>9</v>
       </c>
       <c r="D88" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E88" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F88">
         <v>129.4</v>
@@ -3014,7 +3013,7 @@
         <v>24.3</v>
       </c>
       <c r="H88" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I88" t="s">
         <v>6</v>
@@ -3031,10 +3030,10 @@
         <v>2</v>
       </c>
       <c r="D89" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E89" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F89">
         <v>122.1</v>
@@ -3060,10 +3059,10 @@
         <v>9</v>
       </c>
       <c r="D90" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E90" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F90">
         <v>142.4</v>
@@ -3072,13 +3071,13 @@
         <v>34</v>
       </c>
       <c r="H90" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I90" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>1</v>
       </c>
@@ -3089,10 +3088,10 @@
         <v>2</v>
       </c>
       <c r="D91" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E91" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F91">
         <v>110</v>
@@ -3107,7 +3106,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>1</v>
       </c>
@@ -3118,10 +3117,10 @@
         <v>9</v>
       </c>
       <c r="D92" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E92" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F92">
         <v>126</v>
@@ -3147,10 +3146,10 @@
         <v>9</v>
       </c>
       <c r="D93" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E93" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F93">
         <v>124.3</v>
@@ -3165,7 +3164,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>1</v>
       </c>
@@ -3176,10 +3175,10 @@
         <v>9</v>
       </c>
       <c r="D94" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E94" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F94">
         <v>134.30000000000001</v>
@@ -3194,7 +3193,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>1</v>
       </c>
@@ -3205,10 +3204,10 @@
         <v>9</v>
       </c>
       <c r="D95" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E95" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F95">
         <v>129.4</v>
@@ -3223,7 +3222,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>1</v>
       </c>
@@ -3234,10 +3233,10 @@
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E96" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F96">
         <v>118</v>
@@ -3263,10 +3262,10 @@
         <v>2</v>
       </c>
       <c r="D97" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E97" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F97">
         <v>111.4</v>
@@ -3281,7 +3280,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>1</v>
       </c>
@@ -3292,10 +3291,10 @@
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E98" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F98">
         <v>116</v>
@@ -3310,7 +3309,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>1</v>
       </c>
@@ -3321,10 +3320,10 @@
         <v>2</v>
       </c>
       <c r="D99" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E99" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F99">
         <v>111.7</v>
@@ -3350,10 +3349,10 @@
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E100" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F100">
         <v>136.5</v>
@@ -3379,10 +3378,10 @@
         <v>2</v>
       </c>
       <c r="D101" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E101" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F101">
         <v>130.5</v>
@@ -3391,13 +3390,13 @@
         <v>18.7</v>
       </c>
       <c r="H101" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I101" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>1</v>
       </c>
@@ -3408,10 +3407,10 @@
         <v>2</v>
       </c>
       <c r="D102" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E102" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F102">
         <v>132.19999999999999</v>
@@ -3437,10 +3436,10 @@
         <v>2</v>
       </c>
       <c r="D103" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E103" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F103">
         <v>122.8</v>
@@ -3466,10 +3465,10 @@
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E104" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F104">
         <v>123.5</v>
@@ -3478,15 +3477,15 @@
         <v>28.4</v>
       </c>
       <c r="H104" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I104" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B105">
         <v>10</v>
@@ -3495,10 +3494,10 @@
         <v>2</v>
       </c>
       <c r="D105" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E105" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F105">
         <v>136.6</v>
@@ -3515,7 +3514,7 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B106">
         <v>10</v>
@@ -3524,10 +3523,10 @@
         <v>2</v>
       </c>
       <c r="D106" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E106" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F106">
         <v>127.5</v>
@@ -3536,7 +3535,7 @@
         <v>25.9</v>
       </c>
       <c r="H106" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I106" t="s">
         <v>6</v>
@@ -3544,7 +3543,7 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B107">
         <v>10</v>
@@ -3553,10 +3552,10 @@
         <v>2</v>
       </c>
       <c r="D107" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E107" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F107">
         <v>137.19999999999999</v>
@@ -3565,7 +3564,7 @@
         <v>33.299999999999997</v>
       </c>
       <c r="H107" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I107" t="s">
         <v>6</v>
@@ -3573,7 +3572,7 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B108">
         <v>10</v>
@@ -3582,10 +3581,10 @@
         <v>2</v>
       </c>
       <c r="D108" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E108" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F108">
         <v>133</v>
@@ -3600,9 +3599,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B109">
         <v>10</v>
@@ -3611,10 +3610,10 @@
         <v>2</v>
       </c>
       <c r="D109" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E109" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F109">
         <v>153.80000000000001</v>
@@ -3629,9 +3628,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B110">
         <v>10</v>
@@ -3640,10 +3639,10 @@
         <v>2</v>
       </c>
       <c r="D110" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E110" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F110">
         <v>130.5</v>
@@ -3658,9 +3657,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B111">
         <v>10</v>
@@ -3669,10 +3668,10 @@
         <v>2</v>
       </c>
       <c r="D111" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E111" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F111">
         <v>140.4</v>
@@ -3687,9 +3686,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B112">
         <v>10</v>
@@ -3698,10 +3697,10 @@
         <v>2</v>
       </c>
       <c r="D112" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E112" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F112">
         <v>144.5</v>
@@ -3718,7 +3717,7 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B113">
         <v>10</v>
@@ -3727,10 +3726,10 @@
         <v>2</v>
       </c>
       <c r="D113" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E113" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F113">
         <v>130</v>
@@ -3745,9 +3744,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B114">
         <v>9</v>
@@ -3756,10 +3755,10 @@
         <v>2</v>
       </c>
       <c r="D114" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E114" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F114">
         <v>138.19999999999999</v>
@@ -3768,15 +3767,15 @@
         <v>31.1</v>
       </c>
       <c r="H114" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I114" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B115">
         <v>10</v>
@@ -3785,10 +3784,10 @@
         <v>2</v>
       </c>
       <c r="D115" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E115" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F115">
         <v>128.19999999999999</v>
@@ -3803,9 +3802,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B116">
         <v>10</v>
@@ -3814,10 +3813,10 @@
         <v>2</v>
       </c>
       <c r="D116" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E116" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F116">
         <v>145</v>
@@ -3826,7 +3825,7 @@
         <v>44.2</v>
       </c>
       <c r="H116" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I116" t="s">
         <v>7</v>
@@ -3834,7 +3833,7 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B117">
         <v>10</v>
@@ -3843,10 +3842,10 @@
         <v>2</v>
       </c>
       <c r="D117" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E117" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F117">
         <v>140.80000000000001</v>
@@ -3858,12 +3857,12 @@
         <v>4</v>
       </c>
       <c r="I117" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B118">
         <v>10</v>
@@ -3872,10 +3871,10 @@
         <v>2</v>
       </c>
       <c r="D118" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E118" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F118">
         <v>131.80000000000001</v>
@@ -3892,7 +3891,7 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B119">
         <v>7</v>
@@ -3901,10 +3900,10 @@
         <v>2</v>
       </c>
       <c r="D119" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E119" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F119">
         <v>138.19999999999999</v>
@@ -3916,12 +3915,12 @@
         <v>4</v>
       </c>
       <c r="I119" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B120">
         <v>11</v>
@@ -3930,10 +3929,10 @@
         <v>2</v>
       </c>
       <c r="D120" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E120" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F120">
         <v>146.9</v>
@@ -3942,15 +3941,15 @@
         <v>35.4</v>
       </c>
       <c r="H120" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I120" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B121">
         <v>6</v>
@@ -3959,10 +3958,10 @@
         <v>2</v>
       </c>
       <c r="D121" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E121" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F121">
         <v>132.19999999999999</v>
@@ -3977,9 +3976,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B122">
         <v>7</v>
@@ -3988,10 +3987,10 @@
         <v>2</v>
       </c>
       <c r="D122" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E122" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F122">
         <v>132.19999999999999</v>
@@ -4006,9 +4005,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B123">
         <v>6</v>
@@ -4017,10 +4016,10 @@
         <v>2</v>
       </c>
       <c r="D123" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E123" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F123">
         <v>126.4</v>
@@ -4037,7 +4036,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B124">
         <v>11</v>
@@ -4046,10 +4045,10 @@
         <v>2</v>
       </c>
       <c r="D124" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E124" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F124">
         <v>146.19999999999999</v>
@@ -4066,7 +4065,7 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B125">
         <v>11</v>
@@ -4075,10 +4074,10 @@
         <v>2</v>
       </c>
       <c r="D125" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E125" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F125">
         <v>144.4</v>
@@ -4087,15 +4086,15 @@
         <v>32.5</v>
       </c>
       <c r="H125" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I125" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B126">
         <v>11</v>
@@ -4104,10 +4103,10 @@
         <v>2</v>
       </c>
       <c r="D126" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E126" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F126">
         <v>142</v>
@@ -4122,9 +4121,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B127">
         <v>8</v>
@@ -4133,10 +4132,10 @@
         <v>2</v>
       </c>
       <c r="D127" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E127" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F127">
         <v>122.6</v>
@@ -4145,15 +4144,15 @@
         <v>34.299999999999997</v>
       </c>
       <c r="H127" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I127" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B128">
         <v>11</v>
@@ -4162,10 +4161,10 @@
         <v>2</v>
       </c>
       <c r="D128" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E128" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F128">
         <v>149</v>
@@ -4174,15 +4173,15 @@
         <v>38.200000000000003</v>
       </c>
       <c r="H128" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I128" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B129">
         <v>10</v>
@@ -4191,10 +4190,10 @@
         <v>2</v>
       </c>
       <c r="D129" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E129" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F129">
         <v>154.69999999999999</v>
@@ -4209,9 +4208,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B130">
         <v>6</v>
@@ -4220,10 +4219,10 @@
         <v>2</v>
       </c>
       <c r="D130" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E130" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F130">
         <v>141.1</v>
@@ -4238,9 +4237,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B131">
         <v>10</v>
@@ -4249,10 +4248,10 @@
         <v>2</v>
       </c>
       <c r="D131" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E131" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F131">
         <v>136.9</v>
@@ -4267,9 +4266,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B132">
         <v>10</v>
@@ -4278,10 +4277,10 @@
         <v>2</v>
       </c>
       <c r="D132" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E132" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F132">
         <v>145.5</v>
@@ -4298,7 +4297,7 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B133">
         <v>11</v>
@@ -4307,10 +4306,10 @@
         <v>2</v>
       </c>
       <c r="D133" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E133" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F133">
         <v>142</v>
@@ -4319,15 +4318,15 @@
         <v>34.6</v>
       </c>
       <c r="H133" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I133" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B134">
         <v>9</v>
@@ -4336,10 +4335,10 @@
         <v>2</v>
       </c>
       <c r="D134" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E134" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F134">
         <v>135.9</v>
@@ -4348,15 +4347,15 @@
         <v>27.4</v>
       </c>
       <c r="H134" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I134" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B135">
         <v>9</v>
@@ -4365,10 +4364,10 @@
         <v>2</v>
       </c>
       <c r="D135" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E135" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F135">
         <v>120.7</v>
@@ -4377,15 +4376,15 @@
         <v>25.3</v>
       </c>
       <c r="H135" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I135" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B136">
         <v>11</v>
@@ -4394,10 +4393,10 @@
         <v>2</v>
       </c>
       <c r="D136" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E136" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F136">
         <v>143.6</v>
@@ -4406,15 +4405,15 @@
         <v>40.700000000000003</v>
       </c>
       <c r="H136" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I136" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B137">
         <v>8</v>
@@ -4423,10 +4422,10 @@
         <v>2</v>
       </c>
       <c r="D137" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E137" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F137">
         <v>127.7</v>
@@ -4443,7 +4442,7 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B138">
         <v>10</v>
@@ -4452,10 +4451,10 @@
         <v>2</v>
       </c>
       <c r="D138" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E138" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F138">
         <v>131.9</v>
@@ -4464,7 +4463,7 @@
         <v>25.5</v>
       </c>
       <c r="H138" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I138" t="s">
         <v>6</v>
@@ -4472,7 +4471,7 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B139">
         <v>10</v>
@@ -4481,10 +4480,10 @@
         <v>2</v>
       </c>
       <c r="D139" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E139" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F139">
         <v>139.6</v>
@@ -4501,7 +4500,7 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B140">
         <v>9</v>
@@ -4510,10 +4509,10 @@
         <v>2</v>
       </c>
       <c r="D140" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E140" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F140">
         <v>137</v>
@@ -4528,9 +4527,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B141">
         <v>10</v>
@@ -4539,10 +4538,10 @@
         <v>2</v>
       </c>
       <c r="D141" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E141" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F141">
         <v>137</v>
@@ -4557,9 +4556,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B142">
         <v>11</v>
@@ -4568,10 +4567,10 @@
         <v>2</v>
       </c>
       <c r="D142" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E142" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F142">
         <v>143.30000000000001</v>
@@ -4586,9 +4585,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B143">
         <v>9</v>
@@ -4597,10 +4596,10 @@
         <v>2</v>
       </c>
       <c r="D143" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E143" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F143">
         <v>129.4</v>
@@ -4609,15 +4608,15 @@
         <v>25.8</v>
       </c>
       <c r="H143" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I143" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B144">
         <v>10</v>
@@ -4626,10 +4625,10 @@
         <v>2</v>
       </c>
       <c r="D144" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E144" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F144">
         <v>127.2</v>
@@ -4646,7 +4645,7 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B145">
         <v>11</v>
@@ -4655,10 +4654,10 @@
         <v>2</v>
       </c>
       <c r="D145" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E145" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F145">
         <v>145.19999999999999</v>
@@ -4673,9 +4672,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B146">
         <v>11</v>
@@ -4684,10 +4683,10 @@
         <v>2</v>
       </c>
       <c r="D146" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E146" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F146">
         <v>140.4</v>
@@ -4702,9 +4701,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B147">
         <v>7</v>
@@ -4713,10 +4712,10 @@
         <v>2</v>
       </c>
       <c r="D147" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E147" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F147">
         <v>146.6</v>
@@ -4731,9 +4730,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B148">
         <v>6</v>
@@ -4742,10 +4741,10 @@
         <v>2</v>
       </c>
       <c r="D148" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E148" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F148">
         <v>135.5</v>
@@ -4760,9 +4759,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B149">
         <v>8</v>
@@ -4771,10 +4770,10 @@
         <v>2</v>
       </c>
       <c r="D149" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E149" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F149">
         <v>125.7</v>
@@ -4789,9 +4788,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B150">
         <v>10</v>
@@ -4800,10 +4799,10 @@
         <v>2</v>
       </c>
       <c r="D150" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E150" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F150">
         <v>137.4</v>
@@ -4818,9 +4817,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B151">
         <v>11</v>
@@ -4829,10 +4828,10 @@
         <v>2</v>
       </c>
       <c r="D151" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E151" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F151">
         <v>153.19999999999999</v>
@@ -4847,9 +4846,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B152">
         <v>11</v>
@@ -4858,10 +4857,10 @@
         <v>2</v>
       </c>
       <c r="D152" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E152" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F152">
         <v>149.19999999999999</v>
@@ -4878,7 +4877,7 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B153">
         <v>10</v>
@@ -4887,10 +4886,10 @@
         <v>2</v>
       </c>
       <c r="D153" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E153" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F153">
         <v>141.30000000000001</v>
@@ -4907,7 +4906,7 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B154">
         <v>5</v>
@@ -4916,10 +4915,10 @@
         <v>2</v>
       </c>
       <c r="D154" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E154" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F154">
         <v>139.6</v>
@@ -4936,7 +4935,7 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B155">
         <v>6</v>
@@ -4945,10 +4944,10 @@
         <v>2</v>
       </c>
       <c r="D155" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E155" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F155">
         <v>134.19999999999999</v>
@@ -4965,7 +4964,7 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B156">
         <v>11</v>
@@ -4974,10 +4973,10 @@
         <v>2</v>
       </c>
       <c r="D156" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E156" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F156">
         <v>146.80000000000001</v>
@@ -4994,7 +4993,7 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B157">
         <v>11</v>
@@ -5003,10 +5002,10 @@
         <v>2</v>
       </c>
       <c r="D157" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E157" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F157">
         <v>146.80000000000001</v>
@@ -5023,7 +5022,7 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B158">
         <v>11</v>
@@ -5032,10 +5031,10 @@
         <v>2</v>
       </c>
       <c r="D158" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E158" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F158">
         <v>144</v>
@@ -5050,9 +5049,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B159">
         <v>6</v>
@@ -5061,10 +5060,10 @@
         <v>2</v>
       </c>
       <c r="D159" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E159" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F159">
         <v>140</v>
@@ -5079,9 +5078,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B160">
         <v>7</v>
@@ -5090,10 +5089,10 @@
         <v>2</v>
       </c>
       <c r="D160" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E160" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F160">
         <v>132.19999999999999</v>
@@ -5108,9 +5107,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B161">
         <v>8</v>
@@ -5119,10 +5118,10 @@
         <v>2</v>
       </c>
       <c r="D161" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E161" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F161">
         <v>132.5</v>
@@ -5139,7 +5138,7 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B162">
         <v>5</v>
@@ -5148,10 +5147,10 @@
         <v>2</v>
       </c>
       <c r="D162" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E162" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F162">
         <v>147</v>
@@ -5163,12 +5162,12 @@
         <v>4</v>
       </c>
       <c r="I162" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B163">
         <v>9</v>
@@ -5177,10 +5176,10 @@
         <v>2</v>
       </c>
       <c r="D163" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E163" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F163">
         <v>135.80000000000001</v>
@@ -5192,12 +5191,12 @@
         <v>4</v>
       </c>
       <c r="I163" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B164">
         <v>5</v>
@@ -5206,10 +5205,10 @@
         <v>2</v>
       </c>
       <c r="D164" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E164" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F164">
         <v>146.1</v>
@@ -5226,7 +5225,7 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B165">
         <v>9</v>
@@ -5235,10 +5234,10 @@
         <v>2</v>
       </c>
       <c r="D165" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E165" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F165">
         <v>126.3</v>
@@ -5253,9 +5252,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B166">
         <v>10</v>
@@ -5264,10 +5263,10 @@
         <v>2</v>
       </c>
       <c r="D166" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E166" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F166">
         <v>141.19999999999999</v>
@@ -5276,15 +5275,15 @@
         <v>29.5</v>
       </c>
       <c r="H166" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I166" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B167">
         <v>11</v>
@@ -5293,10 +5292,10 @@
         <v>2</v>
       </c>
       <c r="D167" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E167" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F167">
         <v>145.5</v>
@@ -5313,7 +5312,7 @@
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B168">
         <v>11</v>
@@ -5322,10 +5321,10 @@
         <v>2</v>
       </c>
       <c r="D168" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E168" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F168">
         <v>144.6</v>
@@ -5342,7 +5341,7 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B169">
         <v>6</v>
@@ -5351,10 +5350,10 @@
         <v>2</v>
       </c>
       <c r="D169" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E169" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F169">
         <v>144.9</v>
@@ -5369,9 +5368,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B170">
         <v>9</v>
@@ -5380,10 +5379,10 @@
         <v>2</v>
       </c>
       <c r="D170" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E170" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F170">
         <v>133.6</v>
@@ -5400,7 +5399,7 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B171">
         <v>9</v>
@@ -5409,10 +5408,10 @@
         <v>2</v>
       </c>
       <c r="D171" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E171" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F171">
         <v>127.9</v>
@@ -5427,9 +5426,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B172">
         <v>9</v>
@@ -5438,10 +5437,10 @@
         <v>2</v>
       </c>
       <c r="D172" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E172" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F172">
         <v>133</v>
@@ -5458,7 +5457,7 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B173">
         <v>11</v>
@@ -5467,10 +5466,10 @@
         <v>2</v>
       </c>
       <c r="D173" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E173" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F173">
         <v>147.19999999999999</v>
@@ -5487,7 +5486,7 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B174">
         <v>8</v>
@@ -5496,10 +5495,10 @@
         <v>2</v>
       </c>
       <c r="D174" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E174" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F174">
         <v>121.3</v>
@@ -5508,15 +5507,15 @@
         <v>29.4</v>
       </c>
       <c r="H174" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I174" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B175">
         <v>10</v>
@@ -5525,10 +5524,10 @@
         <v>2</v>
       </c>
       <c r="D175" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E175" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F175">
         <v>142</v>
@@ -5543,9 +5542,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B176">
         <v>6</v>
@@ -5554,10 +5553,10 @@
         <v>2</v>
       </c>
       <c r="D176" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E176" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F176">
         <v>134.80000000000001</v>
@@ -5574,7 +5573,7 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B177">
         <v>11</v>
@@ -5583,10 +5582,10 @@
         <v>2</v>
       </c>
       <c r="D177" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E177" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F177">
         <v>150.19999999999999</v>
@@ -5595,15 +5594,15 @@
         <v>44.4</v>
       </c>
       <c r="H177" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I177" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B178">
         <v>11</v>
@@ -5612,10 +5611,10 @@
         <v>2</v>
       </c>
       <c r="D178" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E178" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F178">
         <v>146.30000000000001</v>
@@ -5630,9 +5629,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B179">
         <v>10</v>
@@ -5641,10 +5640,10 @@
         <v>2</v>
       </c>
       <c r="D179" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E179" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F179">
         <v>141.1</v>
@@ -5653,15 +5652,15 @@
         <v>32.299999999999997</v>
       </c>
       <c r="H179" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I179" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B180">
         <v>10</v>
@@ -5670,10 +5669,10 @@
         <v>2</v>
       </c>
       <c r="D180" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E180" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F180">
         <v>141.80000000000001</v>
@@ -5688,9 +5687,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B181">
         <v>11</v>
@@ -5699,10 +5698,10 @@
         <v>2</v>
       </c>
       <c r="D181" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E181" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F181">
         <v>148.1</v>
@@ -5717,9 +5716,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B182">
         <v>11</v>
@@ -5728,10 +5727,10 @@
         <v>2</v>
       </c>
       <c r="D182" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E182" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F182">
         <v>143.4</v>
@@ -5746,9 +5745,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B183">
         <v>6</v>
@@ -5757,10 +5756,10 @@
         <v>2</v>
       </c>
       <c r="D183" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E183" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F183">
         <v>133.30000000000001</v>
@@ -5775,9 +5774,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B184">
         <v>10</v>
@@ -5786,10 +5785,10 @@
         <v>2</v>
       </c>
       <c r="D184" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E184" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F184">
         <v>133.1</v>
@@ -5804,9 +5803,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B185">
         <v>12</v>
@@ -5815,10 +5814,10 @@
         <v>2</v>
       </c>
       <c r="D185" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E185" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F185">
         <v>143.80000000000001</v>
@@ -5833,9 +5832,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B186">
         <v>8</v>
@@ -5844,10 +5843,10 @@
         <v>2</v>
       </c>
       <c r="D186" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E186" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F186">
         <v>137.4</v>
@@ -5864,7 +5863,7 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B187">
         <v>11</v>
@@ -5873,10 +5872,10 @@
         <v>2</v>
       </c>
       <c r="D187" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E187" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F187">
         <v>136.30000000000001</v>
@@ -5893,7 +5892,7 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B188">
         <v>12</v>
@@ -5902,10 +5901,10 @@
         <v>2</v>
       </c>
       <c r="D188" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E188" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F188">
         <v>143.6</v>
@@ -5920,9 +5919,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B189">
         <v>11</v>
@@ -5931,10 +5930,10 @@
         <v>2</v>
       </c>
       <c r="D189" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E189" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F189">
         <v>142.69999999999999</v>
@@ -5951,7 +5950,7 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B190">
         <v>6</v>
@@ -5960,10 +5959,10 @@
         <v>2</v>
       </c>
       <c r="D190" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E190" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F190">
         <v>135.69999999999999</v>
@@ -5980,7 +5979,7 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B191">
         <v>10</v>
@@ -5989,10 +5988,10 @@
         <v>2</v>
       </c>
       <c r="D191" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E191" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F191">
         <v>134.19999999999999</v>
@@ -6001,7 +6000,7 @@
         <v>37.299999999999997</v>
       </c>
       <c r="H191" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I191" t="s">
         <v>6</v>
@@ -6009,7 +6008,7 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B192">
         <v>10</v>
@@ -6018,10 +6017,10 @@
         <v>2</v>
       </c>
       <c r="D192" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E192" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F192">
         <v>137.19999999999999</v>
@@ -6036,9 +6035,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B193">
         <v>9</v>
@@ -6047,10 +6046,10 @@
         <v>2</v>
       </c>
       <c r="D193" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E193" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F193">
         <v>130.1</v>
@@ -6065,9 +6064,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B194">
         <v>7</v>
@@ -6076,10 +6075,10 @@
         <v>2</v>
       </c>
       <c r="D194" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E194" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F194">
         <v>134.6</v>
@@ -6094,9 +6093,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B195">
         <v>11</v>
@@ -6105,10 +6104,10 @@
         <v>2</v>
       </c>
       <c r="D195" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E195" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F195">
         <v>147.6</v>
@@ -6123,9 +6122,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B196">
         <v>7</v>
@@ -6134,10 +6133,10 @@
         <v>2</v>
       </c>
       <c r="D196" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E196" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F196">
         <v>145</v>
@@ -6152,9 +6151,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B197">
         <v>11</v>
@@ -6163,10 +6162,10 @@
         <v>2</v>
       </c>
       <c r="D197" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E197" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F197">
         <v>149.69999999999999</v>
@@ -6181,9 +6180,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B198">
         <v>11</v>
@@ -6192,10 +6191,10 @@
         <v>2</v>
       </c>
       <c r="D198" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E198" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F198">
         <v>142</v>
@@ -6210,9 +6209,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B199">
         <v>7</v>
@@ -6221,10 +6220,10 @@
         <v>2</v>
       </c>
       <c r="D199" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E199" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F199">
         <v>142.1</v>
@@ -6239,9 +6238,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B200">
         <v>9</v>
@@ -6250,10 +6249,10 @@
         <v>2</v>
       </c>
       <c r="D200" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E200" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F200">
         <v>126</v>
@@ -6268,9 +6267,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B201">
         <v>0</v>
@@ -6279,10 +6278,10 @@
         <v>2</v>
       </c>
       <c r="D201" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E201" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F201">
         <v>134.80000000000001</v>
@@ -6297,9 +6296,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B202">
         <v>10</v>
@@ -6308,10 +6307,10 @@
         <v>2</v>
       </c>
       <c r="D202" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E202" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F202">
         <v>134.80000000000001</v>
@@ -6326,9 +6325,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B203">
         <v>11</v>
@@ -6337,10 +6336,10 @@
         <v>2</v>
       </c>
       <c r="D203" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E203" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F203">
         <v>133.4</v>
@@ -6349,15 +6348,15 @@
         <v>30.4</v>
       </c>
       <c r="H203" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I203" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B204">
         <v>11</v>
@@ -6366,10 +6365,10 @@
         <v>2</v>
       </c>
       <c r="D204" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E204" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F204">
         <v>144.9</v>
@@ -6384,9 +6383,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B205">
         <v>11</v>
@@ -6395,10 +6394,10 @@
         <v>2</v>
       </c>
       <c r="D205" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E205" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F205">
         <v>149.19999999999999</v>
@@ -6413,9 +6412,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B206">
         <v>12</v>
@@ -6424,10 +6423,10 @@
         <v>2</v>
       </c>
       <c r="D206" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E206" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F206">
         <v>141</v>
@@ -6444,7 +6443,7 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B207">
         <v>12</v>
@@ -6453,10 +6452,10 @@
         <v>2</v>
       </c>
       <c r="D207" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E207" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F207">
         <v>147.5</v>
@@ -6465,7 +6464,7 @@
         <v>33.9</v>
       </c>
       <c r="H207" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I207" t="s">
         <v>6</v>
@@ -6473,7 +6472,7 @@
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B208">
         <v>12</v>
@@ -6482,10 +6481,10 @@
         <v>2</v>
       </c>
       <c r="D208" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E208" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F208">
         <v>142.30000000000001</v>
@@ -6494,15 +6493,15 @@
         <v>28.9</v>
       </c>
       <c r="H208" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I208" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B209">
         <v>9</v>
@@ -6511,10 +6510,10 @@
         <v>2</v>
       </c>
       <c r="D209" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E209" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F209">
         <v>132.30000000000001</v>
@@ -6529,9 +6528,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B210">
         <v>9</v>
@@ -6540,10 +6539,10 @@
         <v>2</v>
       </c>
       <c r="D210" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E210" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F210">
         <v>132.19999999999999</v>
@@ -6558,9 +6557,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B211">
         <v>10</v>
@@ -6569,10 +6568,10 @@
         <v>2</v>
       </c>
       <c r="D211" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E211" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F211">
         <v>139.1</v>
@@ -6587,9 +6586,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B212">
         <v>11</v>
@@ -6598,10 +6597,10 @@
         <v>2</v>
       </c>
       <c r="D212" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E212" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F212">
         <v>137.9</v>
@@ -6616,9 +6615,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B213">
         <v>9</v>
@@ -6627,10 +6626,10 @@
         <v>2</v>
       </c>
       <c r="D213" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E213" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F213">
         <v>134.6</v>
@@ -6645,9 +6644,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B214">
         <v>10</v>
@@ -6656,10 +6655,10 @@
         <v>2</v>
       </c>
       <c r="D214" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E214" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F214">
         <v>134.30000000000001</v>
@@ -6675,7 +6674,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I214" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I214" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="Bajo"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6687,27 +6692,27 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
